--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 29,06,26 бррсч ост ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 29,06,26 бррсч ост ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36C4633-EC77-4255-9CDF-B9EB3F46822A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC924CBE-64EE-4482-B3A7-FE29267C28D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,20 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AC$106</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="146">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -414,9 +406,6 @@
     <t>7288 БАЛЫК с/к с/н в/у 1/100 10шт ОСТАНКИНО</t>
   </si>
   <si>
-    <t>новинка</t>
-  </si>
-  <si>
     <t>7332 БОЯРСКАЯ ПМ п/к в/у 0,28кг ОСТАНКИНО</t>
   </si>
   <si>
@@ -461,6 +450,56 @@
   <si>
     <t>бонус</t>
   </si>
+  <si>
+    <t>ротация</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>нужно увеличить продажи!!!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> / ротация на 7539</t>
+    </r>
+  </si>
+  <si>
+    <t>нужно увеличить продажи</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>нужно увеличить продажи!!!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> / вместо 6324</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -469,7 +508,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,6 +554,13 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -596,7 +642,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -612,8 +658,26 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -934,7 +998,7 @@
     <col min="20" max="20" width="21" customWidth="1"/>
     <col min="21" max="22" width="5" customWidth="1"/>
     <col min="23" max="27" width="6" customWidth="1"/>
-    <col min="28" max="28" width="32" customWidth="1"/>
+    <col min="28" max="28" width="32" style="22" customWidth="1"/>
     <col min="29" max="29" width="7" customWidth="1"/>
     <col min="30" max="50" width="3" customWidth="1"/>
   </cols>
@@ -967,7 +1031,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
+      <c r="AB1" s="17"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -1019,7 +1083,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
+      <c r="AB2" s="17"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
@@ -1125,7 +1189,7 @@
       <c r="AA3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AB3" s="18" t="s">
         <v>22</v>
       </c>
       <c r="AC3" s="2" t="s">
@@ -1197,7 +1261,7 @@
       <c r="AA4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AB4" s="1"/>
+      <c r="AB4" s="17"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
@@ -1228,11 +1292,11 @@
       <c r="D5" s="1"/>
       <c r="E5" s="4">
         <f>SUM(E6:E497)</f>
-        <v>11520.940999999999</v>
+        <v>11528.940999999999</v>
       </c>
       <c r="F5" s="4">
         <f>SUM(F6:F497)</f>
-        <v>13369.787999999997</v>
+        <v>13595.787999999997</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="1"/>
@@ -1244,7 +1308,7 @@
       </c>
       <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>-2156.6669999999999</v>
+        <v>-2148.6669999999999</v>
       </c>
       <c r="M5" s="4">
         <f t="shared" si="0"/>
@@ -1264,7 +1328,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>2304.1881999999996</v>
+        <v>2305.7882</v>
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
@@ -1297,7 +1361,7 @@
         <f>SUM(AA6:AA497)</f>
         <v>2316.4051999999992</v>
       </c>
-      <c r="AB5" s="1"/>
+      <c r="AB5" s="17"/>
       <c r="AC5" s="4">
         <f>SUM(AC6:AC497)</f>
         <v>3768.532400000001</v>
@@ -1397,7 +1461,7 @@
       <c r="AA6" s="1">
         <v>53.6</v>
       </c>
-      <c r="AB6" s="1"/>
+      <c r="AB6" s="17"/>
       <c r="AC6" s="1">
         <f t="shared" ref="AC6:AC35" si="5">G6*R6</f>
         <v>128.16</v>
@@ -1469,7 +1533,7 @@
         <v>4.5156000000000001</v>
       </c>
       <c r="R7" s="5">
-        <f t="shared" ref="R7:R35" si="6">14*Q7-P7-O7-F7</f>
+        <f t="shared" ref="R7:R34" si="6">14*Q7-P7-O7-F7</f>
         <v>34.243400000000001</v>
       </c>
       <c r="S7" s="5"/>
@@ -1497,7 +1561,7 @@
       <c r="AA7" s="1">
         <v>2.7652000000000001</v>
       </c>
-      <c r="AB7" s="1"/>
+      <c r="AB7" s="17"/>
       <c r="AC7" s="1">
         <f t="shared" si="5"/>
         <v>34.243400000000001</v>
@@ -1601,7 +1665,7 @@
       <c r="AA8" s="1">
         <v>30.8</v>
       </c>
-      <c r="AB8" s="1"/>
+      <c r="AB8" s="17"/>
       <c r="AC8" s="1">
         <f t="shared" si="5"/>
         <v>25.649999999999991</v>
@@ -1705,7 +1769,7 @@
       <c r="AA9" s="1">
         <v>55.194800000000001</v>
       </c>
-      <c r="AB9" s="1"/>
+      <c r="AB9" s="17"/>
       <c r="AC9" s="1">
         <f t="shared" si="5"/>
         <v>269.17259999999999</v>
@@ -1809,7 +1873,7 @@
       <c r="AA10" s="1">
         <v>1.2904</v>
       </c>
-      <c r="AB10" s="1"/>
+      <c r="AB10" s="17"/>
       <c r="AC10" s="1">
         <f t="shared" si="5"/>
         <v>18.398399999999999</v>
@@ -1908,7 +1972,7 @@
       <c r="AA11" s="1">
         <v>9.4993999999999996</v>
       </c>
-      <c r="AB11" s="1"/>
+      <c r="AB11" s="17"/>
       <c r="AC11" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -2012,7 +2076,7 @@
       <c r="AA12" s="1">
         <v>47.341200000000001</v>
       </c>
-      <c r="AB12" s="1"/>
+      <c r="AB12" s="17"/>
       <c r="AC12" s="1">
         <f t="shared" si="5"/>
         <v>231.28760000000005</v>
@@ -2116,7 +2180,7 @@
       <c r="AA13" s="1">
         <v>16.8</v>
       </c>
-      <c r="AB13" s="1"/>
+      <c r="AB13" s="17"/>
       <c r="AC13" s="1">
         <f t="shared" si="5"/>
         <v>103.64999999999998</v>
@@ -2162,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="10"/>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="15" t="s">
         <v>67</v>
       </c>
       <c r="J14" s="10" t="s">
@@ -2211,7 +2275,7 @@
       <c r="AA14" s="10">
         <v>0</v>
       </c>
-      <c r="AB14" s="10"/>
+      <c r="AB14" s="19"/>
       <c r="AC14" s="10"/>
       <c r="AD14" s="1"/>
       <c r="AE14" s="1"/>
@@ -2309,7 +2373,7 @@
       <c r="AA15" s="1">
         <v>20.625</v>
       </c>
-      <c r="AB15" s="1"/>
+      <c r="AB15" s="17"/>
       <c r="AC15" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -2413,7 +2477,7 @@
       <c r="AA16" s="1">
         <v>35.6</v>
       </c>
-      <c r="AB16" s="1"/>
+      <c r="AB16" s="17"/>
       <c r="AC16" s="1">
         <f t="shared" si="5"/>
         <v>62.399999999999991</v>
@@ -2517,7 +2581,7 @@
       <c r="AA17" s="1">
         <v>12</v>
       </c>
-      <c r="AB17" s="1"/>
+      <c r="AB17" s="17"/>
       <c r="AC17" s="1">
         <f t="shared" si="5"/>
         <v>48.08</v>
@@ -2621,7 +2685,7 @@
       <c r="AA18" s="1">
         <v>33.668999999999997</v>
       </c>
-      <c r="AB18" s="1" t="s">
+      <c r="AB18" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AC18" s="1">
@@ -2671,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="10"/>
-      <c r="I19" s="16" t="s">
+      <c r="I19" s="15" t="s">
         <v>67</v>
       </c>
       <c r="J19" s="10" t="s">
@@ -2722,7 +2786,7 @@
       <c r="AA19" s="10">
         <v>-0.2</v>
       </c>
-      <c r="AB19" s="10"/>
+      <c r="AB19" s="19"/>
       <c r="AC19" s="10"/>
       <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
@@ -2821,7 +2885,7 @@
       <c r="AA20" s="1">
         <v>2.1798000000000002</v>
       </c>
-      <c r="AB20" s="1"/>
+      <c r="AB20" s="17"/>
       <c r="AC20" s="1">
         <f t="shared" si="5"/>
         <v>24.092800000000004</v>
@@ -2923,7 +2987,7 @@
       <c r="AA21" s="1">
         <v>0</v>
       </c>
-      <c r="AB21" s="1" t="s">
+      <c r="AB21" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AC21" s="1">
@@ -3029,7 +3093,7 @@
       <c r="AA22" s="1">
         <v>28.4008</v>
       </c>
-      <c r="AB22" s="1"/>
+      <c r="AB22" s="17"/>
       <c r="AC22" s="1">
         <f t="shared" si="5"/>
         <v>84.753999999999991</v>
@@ -3133,7 +3197,7 @@
       <c r="AA23" s="1">
         <v>35</v>
       </c>
-      <c r="AB23" s="1"/>
+      <c r="AB23" s="17"/>
       <c r="AC23" s="1">
         <f t="shared" si="5"/>
         <v>40.92</v>
@@ -3232,7 +3296,7 @@
       <c r="AA24" s="1">
         <v>0</v>
       </c>
-      <c r="AB24" s="1"/>
+      <c r="AB24" s="17"/>
       <c r="AC24" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -3332,7 +3396,7 @@
       <c r="AA25" s="1">
         <v>1.4</v>
       </c>
-      <c r="AB25" s="1"/>
+      <c r="AB25" s="17"/>
       <c r="AC25" s="1">
         <f t="shared" si="5"/>
         <v>1.8899999999999997</v>
@@ -3436,7 +3500,7 @@
       <c r="AA26" s="1">
         <v>12.271599999999999</v>
       </c>
-      <c r="AB26" s="1"/>
+      <c r="AB26" s="17"/>
       <c r="AC26" s="1">
         <f t="shared" si="5"/>
         <v>27.418000000000006</v>
@@ -3540,7 +3604,7 @@
       <c r="AA27" s="1">
         <v>23.8</v>
       </c>
-      <c r="AB27" s="1"/>
+      <c r="AB27" s="17"/>
       <c r="AC27" s="1">
         <f t="shared" si="5"/>
         <v>4.7160000000000029</v>
@@ -3644,7 +3708,7 @@
       <c r="AA28" s="1">
         <v>7.4</v>
       </c>
-      <c r="AB28" s="1"/>
+      <c r="AB28" s="17"/>
       <c r="AC28" s="1">
         <f t="shared" si="5"/>
         <v>5.04</v>
@@ -3672,7 +3736,7 @@
       <c r="AX28" s="1"/>
     </row>
     <row r="29" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="15" t="s">
         <v>59</v>
       </c>
       <c r="B29" s="10" t="s">
@@ -3692,11 +3756,11 @@
       <c r="H29" s="10">
         <v>60</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="I29" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J29" s="16" t="s">
-        <v>135</v>
+      <c r="J29" s="15" t="s">
+        <v>134</v>
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="10">
@@ -3741,7 +3805,7 @@
       <c r="AA29" s="10">
         <v>1.8</v>
       </c>
-      <c r="AB29" s="10"/>
+      <c r="AB29" s="19"/>
       <c r="AC29" s="10"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
@@ -3839,7 +3903,7 @@
       <c r="AA30" s="1">
         <v>10.6</v>
       </c>
-      <c r="AB30" s="1"/>
+      <c r="AB30" s="17"/>
       <c r="AC30" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -3943,7 +4007,7 @@
       <c r="AA31" s="1">
         <v>71.153400000000005</v>
       </c>
-      <c r="AB31" s="1"/>
+      <c r="AB31" s="17"/>
       <c r="AC31" s="1">
         <f t="shared" si="5"/>
         <v>276.07099999999997</v>
@@ -3970,85 +4034,84 @@
       <c r="AW31" s="1"/>
       <c r="AX31" s="1"/>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:50" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="10">
         <v>235</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1">
+      <c r="D32" s="10"/>
+      <c r="E32" s="14">
         <v>8</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="14">
         <v>226</v>
       </c>
-      <c r="G32" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="H32" s="1">
+      <c r="G32" s="11">
+        <v>0</v>
+      </c>
+      <c r="H32" s="10">
         <v>60</v>
       </c>
-      <c r="I32" s="1">
-        <v>6324</v>
-      </c>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1">
+      <c r="I32" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="K32" s="10">
         <v>92</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L32" s="10">
         <f t="shared" si="1"/>
         <v>-84</v>
       </c>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1">
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10">
         <v>0</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="10">
         <v>0</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="Q32" s="10">
         <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1">
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10">
         <f t="shared" si="3"/>
         <v>141.25</v>
       </c>
-      <c r="V32" s="1">
+      <c r="V32" s="10">
         <f t="shared" si="4"/>
         <v>141.25</v>
       </c>
-      <c r="W32" s="1">
+      <c r="W32" s="10">
         <v>6.2</v>
       </c>
-      <c r="X32" s="1">
+      <c r="X32" s="10">
         <v>4.2</v>
       </c>
-      <c r="Y32" s="1">
+      <c r="Y32" s="10">
         <v>18.600000000000001</v>
       </c>
-      <c r="Z32" s="1">
+      <c r="Z32" s="10">
         <v>16.600000000000001</v>
       </c>
-      <c r="AA32" s="1">
+      <c r="AA32" s="10">
         <v>9.4</v>
       </c>
-      <c r="AB32" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC32" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="AB32" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC32" s="10"/>
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
@@ -4148,7 +4211,7 @@
       <c r="AA33" s="1">
         <v>22.8</v>
       </c>
-      <c r="AB33" s="1"/>
+      <c r="AB33" s="17"/>
       <c r="AC33" s="1">
         <f t="shared" si="5"/>
         <v>70.239999999999995</v>
@@ -4252,7 +4315,7 @@
       <c r="AA34" s="1">
         <v>73.8</v>
       </c>
-      <c r="AB34" s="1"/>
+      <c r="AB34" s="17"/>
       <c r="AC34" s="1">
         <f t="shared" si="5"/>
         <v>42.800000000000004</v>
@@ -4356,7 +4419,7 @@
       <c r="AA35" s="1">
         <v>67</v>
       </c>
-      <c r="AB35" s="1" t="s">
+      <c r="AB35" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AC35" s="1">
@@ -4453,7 +4516,7 @@
       <c r="AA36" s="10">
         <v>0</v>
       </c>
-      <c r="AB36" s="10"/>
+      <c r="AB36" s="19"/>
       <c r="AC36" s="10"/>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
@@ -4554,7 +4617,7 @@
       <c r="AA37" s="1">
         <v>88.8</v>
       </c>
-      <c r="AB37" s="1" t="s">
+      <c r="AB37" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AC37" s="1">
@@ -4632,7 +4695,7 @@
         <v>49</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" ref="R37:R90" si="10">14*Q38-P38-O38-F38</f>
+        <f t="shared" ref="R38:R90" si="10">14*Q38-P38-O38-F38</f>
         <v>404</v>
       </c>
       <c r="S38" s="5"/>
@@ -4660,7 +4723,7 @@
       <c r="AA38" s="1">
         <v>45.4</v>
       </c>
-      <c r="AB38" s="1" t="s">
+      <c r="AB38" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AC38" s="1">
@@ -4766,7 +4829,7 @@
       <c r="AA39" s="1">
         <v>33.4</v>
       </c>
-      <c r="AB39" s="1"/>
+      <c r="AB39" s="17"/>
       <c r="AC39" s="1">
         <f t="shared" si="7"/>
         <v>10.519999999999994</v>
@@ -4867,7 +4930,7 @@
       <c r="AA40" s="1">
         <v>5.8</v>
       </c>
-      <c r="AB40" s="1"/>
+      <c r="AB40" s="17"/>
       <c r="AC40" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -4964,7 +5027,9 @@
       <c r="AA41" s="1">
         <v>0</v>
       </c>
-      <c r="AB41" s="1"/>
+      <c r="AB41" s="20" t="s">
+        <v>144</v>
+      </c>
       <c r="AC41" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -5063,7 +5128,7 @@
       <c r="AA42" s="1">
         <v>19.8</v>
       </c>
-      <c r="AB42" s="1"/>
+      <c r="AB42" s="17"/>
       <c r="AC42" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -5162,7 +5227,7 @@
       <c r="AA43" s="1">
         <v>0</v>
       </c>
-      <c r="AB43" s="1"/>
+      <c r="AB43" s="17"/>
       <c r="AC43" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -5266,7 +5331,7 @@
       <c r="AA44" s="1">
         <v>22.037800000000001</v>
       </c>
-      <c r="AB44" s="1"/>
+      <c r="AB44" s="17"/>
       <c r="AC44" s="1">
         <f t="shared" si="7"/>
         <v>254.39620000000005</v>
@@ -5370,7 +5435,7 @@
       <c r="AA45" s="1">
         <v>7.4770000000000003</v>
       </c>
-      <c r="AB45" s="1"/>
+      <c r="AB45" s="17"/>
       <c r="AC45" s="1">
         <f t="shared" si="7"/>
         <v>91.421599999999984</v>
@@ -5471,7 +5536,7 @@
       <c r="AA46" s="1">
         <v>11.1358</v>
       </c>
-      <c r="AB46" s="1"/>
+      <c r="AB46" s="17"/>
       <c r="AC46" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -5568,7 +5633,7 @@
       <c r="AA47" s="1">
         <v>0</v>
       </c>
-      <c r="AB47" s="15" t="s">
+      <c r="AB47" s="21" t="s">
         <v>36</v>
       </c>
       <c r="AC47" s="1">
@@ -5671,7 +5736,7 @@
       <c r="AA48" s="1">
         <v>6.4436</v>
       </c>
-      <c r="AB48" s="1" t="s">
+      <c r="AB48" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AC48" s="1">
@@ -5777,7 +5842,7 @@
       <c r="AA49" s="1">
         <v>64.2</v>
       </c>
-      <c r="AB49" s="1"/>
+      <c r="AB49" s="17"/>
       <c r="AC49" s="1">
         <f t="shared" si="7"/>
         <v>12.54000000000002</v>
@@ -5878,7 +5943,9 @@
       <c r="AA50" s="1">
         <v>1.7096</v>
       </c>
-      <c r="AB50" s="1"/>
+      <c r="AB50" s="20" t="s">
+        <v>144</v>
+      </c>
       <c r="AC50" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -5982,7 +6049,7 @@
       <c r="AA51" s="1">
         <v>113.4</v>
       </c>
-      <c r="AB51" s="1" t="s">
+      <c r="AB51" s="17" t="s">
         <v>84</v>
       </c>
       <c r="AC51" s="1">
@@ -6085,7 +6152,7 @@
       <c r="AA52" s="1">
         <v>39.4</v>
       </c>
-      <c r="AB52" s="1"/>
+      <c r="AB52" s="17"/>
       <c r="AC52" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6186,7 +6253,7 @@
       <c r="AA53" s="1">
         <v>40.799999999999997</v>
       </c>
-      <c r="AB53" s="1"/>
+      <c r="AB53" s="17"/>
       <c r="AC53" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6281,7 +6348,7 @@
       <c r="AA54" s="1">
         <v>0</v>
       </c>
-      <c r="AB54" s="15" t="s">
+      <c r="AB54" s="21" t="s">
         <v>36</v>
       </c>
       <c r="AC54" s="1">
@@ -6382,7 +6449,7 @@
       <c r="AA55" s="1">
         <v>8.6</v>
       </c>
-      <c r="AB55" s="1" t="s">
+      <c r="AB55" s="17" t="s">
         <v>48</v>
       </c>
       <c r="AC55" s="1">
@@ -6479,7 +6546,7 @@
       <c r="AA56" s="1">
         <v>0.87439999999999996</v>
       </c>
-      <c r="AB56" s="1"/>
+      <c r="AB56" s="17"/>
       <c r="AC56" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6580,7 +6647,7 @@
       <c r="AA57" s="1">
         <v>3.6</v>
       </c>
-      <c r="AB57" s="1"/>
+      <c r="AB57" s="17"/>
       <c r="AC57" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6630,11 +6697,11 @@
       <c r="H58" s="10">
         <v>0</v>
       </c>
-      <c r="I58" s="16" t="s">
+      <c r="I58" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J58" s="16" t="s">
-        <v>137</v>
+      <c r="J58" s="15" t="s">
+        <v>136</v>
       </c>
       <c r="K58" s="10">
         <v>141</v>
@@ -6681,7 +6748,7 @@
       <c r="AA58" s="10">
         <v>27.4</v>
       </c>
-      <c r="AB58" s="10"/>
+      <c r="AB58" s="19"/>
       <c r="AC58" s="10"/>
       <c r="AD58" s="1"/>
       <c r="AE58" s="1"/>
@@ -6777,7 +6844,9 @@
       <c r="AA59" s="1">
         <v>0</v>
       </c>
-      <c r="AB59" s="1"/>
+      <c r="AB59" s="20" t="s">
+        <v>144</v>
+      </c>
       <c r="AC59" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6876,8 +6945,8 @@
       <c r="AA60" s="1">
         <v>11.8</v>
       </c>
-      <c r="AB60" s="1" t="s">
-        <v>48</v>
+      <c r="AB60" s="21" t="s">
+        <v>36</v>
       </c>
       <c r="AC60" s="1">
         <f t="shared" si="7"/>
@@ -6982,7 +7051,7 @@
       <c r="AA61" s="1">
         <v>31.852</v>
       </c>
-      <c r="AB61" s="1"/>
+      <c r="AB61" s="17"/>
       <c r="AC61" s="1">
         <f t="shared" si="7"/>
         <v>136.60219999999998</v>
@@ -7081,7 +7150,9 @@
       <c r="AA62" s="1">
         <v>-0.2</v>
       </c>
-      <c r="AB62" s="1"/>
+      <c r="AB62" s="20" t="s">
+        <v>144</v>
+      </c>
       <c r="AC62" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -7182,7 +7253,7 @@
       <c r="AA63" s="1">
         <v>19.399999999999999</v>
       </c>
-      <c r="AB63" s="1"/>
+      <c r="AB63" s="17"/>
       <c r="AC63" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -7279,7 +7350,7 @@
       <c r="AA64" s="1">
         <v>1.8169999999999999</v>
       </c>
-      <c r="AB64" s="1" t="s">
+      <c r="AB64" s="17" t="s">
         <v>98</v>
       </c>
       <c r="AC64" s="1">
@@ -7380,7 +7451,9 @@
       <c r="AA65" s="1">
         <v>5.8</v>
       </c>
-      <c r="AB65" s="1"/>
+      <c r="AB65" s="20" t="s">
+        <v>144</v>
+      </c>
       <c r="AC65" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -7475,7 +7548,7 @@
       <c r="AA66" s="10">
         <v>0</v>
       </c>
-      <c r="AB66" s="10"/>
+      <c r="AB66" s="19"/>
       <c r="AC66" s="10"/>
       <c r="AD66" s="1"/>
       <c r="AE66" s="1"/>
@@ -7576,7 +7649,7 @@
       <c r="AA67" s="1">
         <v>9.4</v>
       </c>
-      <c r="AB67" s="1"/>
+      <c r="AB67" s="17"/>
       <c r="AC67" s="1">
         <f t="shared" si="7"/>
         <v>28.85</v>
@@ -7677,7 +7750,7 @@
       <c r="AA68" s="1">
         <v>3.7509999999999999</v>
       </c>
-      <c r="AB68" s="1"/>
+      <c r="AB68" s="17"/>
       <c r="AC68" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -7776,7 +7849,7 @@
       <c r="AA69" s="1">
         <v>20</v>
       </c>
-      <c r="AB69" s="1"/>
+      <c r="AB69" s="17"/>
       <c r="AC69" s="1">
         <f t="shared" ref="AC69:AC90" si="13">G69*R69</f>
         <v>0</v>
@@ -7881,7 +7954,7 @@
       <c r="AA70" s="1">
         <v>126.6</v>
       </c>
-      <c r="AB70" s="1"/>
+      <c r="AB70" s="17"/>
       <c r="AC70" s="1">
         <f t="shared" si="13"/>
         <v>20.992000000000111</v>
@@ -7982,7 +8055,7 @@
       <c r="AA71" s="1">
         <v>19.577400000000001</v>
       </c>
-      <c r="AB71" s="1"/>
+      <c r="AB71" s="17"/>
       <c r="AC71" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -8086,7 +8159,7 @@
       <c r="AA72" s="1">
         <v>11.2</v>
       </c>
-      <c r="AB72" s="1"/>
+      <c r="AB72" s="17"/>
       <c r="AC72" s="1">
         <f t="shared" si="13"/>
         <v>4.269999999999996</v>
@@ -8190,7 +8263,7 @@
       <c r="AA73" s="1">
         <v>1.0014000000000001</v>
       </c>
-      <c r="AB73" s="1"/>
+      <c r="AB73" s="17"/>
       <c r="AC73" s="1">
         <f t="shared" si="13"/>
         <v>21.390599999999996</v>
@@ -8294,7 +8367,7 @@
       <c r="AA74" s="1">
         <v>126.8</v>
       </c>
-      <c r="AB74" s="1"/>
+      <c r="AB74" s="17"/>
       <c r="AC74" s="1">
         <f t="shared" si="13"/>
         <v>140.79399999999993</v>
@@ -8393,7 +8466,7 @@
       <c r="AA75" s="10">
         <v>0</v>
       </c>
-      <c r="AB75" s="10"/>
+      <c r="AB75" s="19"/>
       <c r="AC75" s="10"/>
       <c r="AD75" s="1"/>
       <c r="AE75" s="1"/>
@@ -8489,7 +8562,7 @@
       <c r="AA76" s="1">
         <v>10.958600000000001</v>
       </c>
-      <c r="AB76" s="1"/>
+      <c r="AB76" s="17"/>
       <c r="AC76" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -8593,7 +8666,7 @@
       <c r="AA77" s="1">
         <v>35.799999999999997</v>
       </c>
-      <c r="AB77" s="1"/>
+      <c r="AB77" s="17"/>
       <c r="AC77" s="1">
         <f t="shared" si="13"/>
         <v>54.6</v>
@@ -8697,7 +8770,7 @@
       <c r="AA78" s="1">
         <v>12.8</v>
       </c>
-      <c r="AB78" s="1"/>
+      <c r="AB78" s="17"/>
       <c r="AC78" s="1">
         <f t="shared" si="13"/>
         <v>29.627999999999993</v>
@@ -8747,11 +8820,11 @@
       <c r="H79" s="10">
         <v>45</v>
       </c>
-      <c r="I79" s="16" t="s">
+      <c r="I79" s="15" t="s">
         <v>67</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K79" s="10">
         <v>35.299999999999997</v>
@@ -8798,7 +8871,7 @@
       <c r="AA79" s="10">
         <v>8.0774000000000008</v>
       </c>
-      <c r="AB79" s="10"/>
+      <c r="AB79" s="19"/>
       <c r="AC79" s="10"/>
       <c r="AD79" s="1"/>
       <c r="AE79" s="1"/>
@@ -8897,7 +8970,7 @@
       <c r="AA80" s="1">
         <v>90.4</v>
       </c>
-      <c r="AB80" s="1"/>
+      <c r="AB80" s="17"/>
       <c r="AC80" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -8998,7 +9071,7 @@
       <c r="AA81" s="1">
         <v>19.853999999999999</v>
       </c>
-      <c r="AB81" s="1"/>
+      <c r="AB81" s="17"/>
       <c r="AC81" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -9102,7 +9175,7 @@
       <c r="AA82" s="1">
         <v>37.647599999999997</v>
       </c>
-      <c r="AB82" s="1"/>
+      <c r="AB82" s="17"/>
       <c r="AC82" s="1">
         <f t="shared" si="13"/>
         <v>130.64140000000003</v>
@@ -9206,7 +9279,7 @@
       <c r="AA83" s="1">
         <v>95.8</v>
       </c>
-      <c r="AB83" s="1"/>
+      <c r="AB83" s="17"/>
       <c r="AC83" s="1">
         <f t="shared" si="13"/>
         <v>76.649999999999991</v>
@@ -9310,7 +9383,7 @@
       <c r="AA84" s="1">
         <v>15.6</v>
       </c>
-      <c r="AB84" s="1"/>
+      <c r="AB84" s="17"/>
       <c r="AC84" s="1">
         <f t="shared" si="13"/>
         <v>28.920000000000009</v>
@@ -9411,7 +9484,9 @@
       <c r="AA85" s="1">
         <v>2</v>
       </c>
-      <c r="AB85" s="1"/>
+      <c r="AB85" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="AC85" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -9515,7 +9590,7 @@
       <c r="AA86" s="1">
         <v>32</v>
       </c>
-      <c r="AB86" s="1"/>
+      <c r="AB86" s="17"/>
       <c r="AC86" s="1">
         <f t="shared" si="13"/>
         <v>59.555999999999983</v>
@@ -9616,7 +9691,7 @@
       <c r="AA87" s="1">
         <v>69.400000000000006</v>
       </c>
-      <c r="AB87" s="1"/>
+      <c r="AB87" s="17"/>
       <c r="AC87" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -9717,7 +9792,7 @@
       <c r="AA88" s="1">
         <v>16.600000000000001</v>
       </c>
-      <c r="AB88" s="1"/>
+      <c r="AB88" s="17"/>
       <c r="AC88" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -9821,7 +9896,7 @@
       <c r="AA89" s="1">
         <v>45</v>
       </c>
-      <c r="AB89" s="1"/>
+      <c r="AB89" s="17"/>
       <c r="AC89" s="1">
         <f t="shared" si="13"/>
         <v>58.744000000000028</v>
@@ -9925,7 +10000,7 @@
       <c r="AA90" s="1">
         <v>95</v>
       </c>
-      <c r="AB90" s="1"/>
+      <c r="AB90" s="17"/>
       <c r="AC90" s="1">
         <f t="shared" si="13"/>
         <v>114.24000000000007</v>
@@ -10016,7 +10091,7 @@
       <c r="AA91" s="10">
         <v>0</v>
       </c>
-      <c r="AB91" s="10"/>
+      <c r="AB91" s="19"/>
       <c r="AC91" s="10"/>
       <c r="AD91" s="1"/>
       <c r="AE91" s="1"/>
@@ -10114,9 +10189,7 @@
       <c r="AA92" s="1">
         <v>6.4</v>
       </c>
-      <c r="AB92" s="1" t="s">
-        <v>127</v>
-      </c>
+      <c r="AB92" s="17"/>
       <c r="AC92" s="1">
         <f t="shared" ref="AC92:AC97" si="18">G92*R92</f>
         <v>0</v>
@@ -10145,7 +10218,7 @@
     </row>
     <row r="93" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>33</v>
@@ -10192,7 +10265,7 @@
         <v>6.4</v>
       </c>
       <c r="R93" s="5">
-        <f t="shared" ref="R92:R97" si="19">14*Q93-P93-O93-F93</f>
+        <f t="shared" ref="R93" si="19">14*Q93-P93-O93-F93</f>
         <v>54.600000000000009</v>
       </c>
       <c r="S93" s="5"/>
@@ -10220,7 +10293,7 @@
       <c r="AA93" s="1">
         <v>11</v>
       </c>
-      <c r="AB93" s="1"/>
+      <c r="AB93" s="17"/>
       <c r="AC93" s="1">
         <f t="shared" si="18"/>
         <v>15.288000000000004</v>
@@ -10249,7 +10322,7 @@
     </row>
     <row r="94" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>33</v>
@@ -10319,7 +10392,7 @@
       <c r="AA94" s="1">
         <v>1.2</v>
       </c>
-      <c r="AB94" s="1"/>
+      <c r="AB94" s="17"/>
       <c r="AC94" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -10348,7 +10421,7 @@
     </row>
     <row r="95" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>33</v>
@@ -10418,7 +10491,9 @@
       <c r="AA95" s="1">
         <v>24.6</v>
       </c>
-      <c r="AB95" s="1"/>
+      <c r="AB95" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="AC95" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -10447,7 +10522,7 @@
     </row>
     <row r="96" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>33</v>
@@ -10519,7 +10594,7 @@
       <c r="AA96" s="1">
         <v>26.6</v>
       </c>
-      <c r="AB96" s="1"/>
+      <c r="AB96" s="17"/>
       <c r="AC96" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -10619,7 +10694,7 @@
       <c r="AA97" s="1">
         <v>30.6</v>
       </c>
-      <c r="AB97" s="1"/>
+      <c r="AB97" s="17"/>
       <c r="AC97" s="1">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -10648,17 +10723,17 @@
     </row>
     <row r="98" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>33</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
-      <c r="E98" s="13">
+      <c r="E98" s="16">
         <v>1</v>
       </c>
-      <c r="F98" s="13">
+      <c r="F98" s="16">
         <v>-1</v>
       </c>
       <c r="G98" s="11">
@@ -10669,7 +10744,7 @@
         <v>67</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K98" s="10">
         <v>3</v>
@@ -10712,7 +10787,7 @@
       <c r="AA98" s="10">
         <v>0</v>
       </c>
-      <c r="AB98" s="10"/>
+      <c r="AB98" s="19"/>
       <c r="AC98" s="10"/>
       <c r="AD98" s="1"/>
       <c r="AE98" s="1"/>
@@ -10738,7 +10813,7 @@
     </row>
     <row r="99" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>33</v>
@@ -10783,7 +10858,7 @@
         <v>15.8</v>
       </c>
       <c r="R99" s="5">
-        <f t="shared" ref="R99:R103" si="20">14*Q99-P99-O99-F99</f>
+        <f t="shared" ref="R99:R100" si="20">14*Q99-P99-O99-F99</f>
         <v>66.200000000000017</v>
       </c>
       <c r="S99" s="5"/>
@@ -10811,7 +10886,7 @@
       <c r="AA99" s="1">
         <v>0</v>
       </c>
-      <c r="AB99" s="1"/>
+      <c r="AB99" s="17"/>
       <c r="AC99" s="1">
         <f>G99*R99</f>
         <v>18.536000000000005</v>
@@ -10840,7 +10915,7 @@
     </row>
     <row r="100" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>33</v>
@@ -10913,7 +10988,7 @@
       <c r="AA100" s="1">
         <v>14</v>
       </c>
-      <c r="AB100" s="1"/>
+      <c r="AB100" s="17"/>
       <c r="AC100" s="1">
         <f>G100*R100</f>
         <v>54.320000000000007</v>
@@ -10940,9 +11015,9 @@
       <c r="AW100" s="1"/>
       <c r="AX100" s="1"/>
     </row>
-    <row r="101" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:50" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>33</v>
@@ -10953,13 +11028,13 @@
       <c r="D101" s="1">
         <v>2</v>
       </c>
-      <c r="E101" s="13">
-        <f>0+E98</f>
-        <v>1</v>
-      </c>
-      <c r="F101" s="13">
-        <f>39+F98</f>
-        <v>38</v>
+      <c r="E101" s="16">
+        <f>0+E98+E32</f>
+        <v>9</v>
+      </c>
+      <c r="F101" s="16">
+        <f>39+F98+F32</f>
+        <v>264</v>
       </c>
       <c r="G101" s="8">
         <v>0.35</v>
@@ -10974,7 +11049,7 @@
       </c>
       <c r="L101" s="1">
         <f t="shared" si="14"/>
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
@@ -10986,18 +11061,18 @@
       </c>
       <c r="Q101" s="1">
         <f t="shared" si="15"/>
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
       <c r="R101" s="5"/>
       <c r="S101" s="5"/>
       <c r="T101" s="1"/>
       <c r="U101" s="1">
         <f t="shared" si="16"/>
-        <v>440</v>
+        <v>174.44444444444443</v>
       </c>
       <c r="V101" s="1">
         <f t="shared" si="17"/>
-        <v>440</v>
+        <v>174.44444444444443</v>
       </c>
       <c r="W101" s="1">
         <v>0.4</v>
@@ -11014,7 +11089,9 @@
       <c r="AA101" s="1">
         <v>0</v>
       </c>
-      <c r="AB101" s="1"/>
+      <c r="AB101" s="20" t="s">
+        <v>145</v>
+      </c>
       <c r="AC101" s="1">
         <f>G101*R101</f>
         <v>0</v>
@@ -11043,7 +11120,7 @@
     </row>
     <row r="102" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>35</v>
@@ -11115,7 +11192,7 @@
       <c r="AA102" s="1">
         <v>0</v>
       </c>
-      <c r="AB102" s="1"/>
+      <c r="AB102" s="17"/>
       <c r="AC102" s="1">
         <f>G102*R102</f>
         <v>0</v>
@@ -11144,7 +11221,7 @@
     </row>
     <row r="103" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>33</v>
@@ -11216,7 +11293,7 @@
       <c r="AA103" s="1">
         <v>0</v>
       </c>
-      <c r="AB103" s="1"/>
+      <c r="AB103" s="17"/>
       <c r="AC103" s="1">
         <f>G103*R103</f>
         <v>0</v>
@@ -11245,7 +11322,7 @@
     </row>
     <row r="104" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>35</v>
@@ -11265,7 +11342,7 @@
       </c>
       <c r="H104" s="10"/>
       <c r="I104" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J104" s="10"/>
       <c r="K104" s="10">
@@ -11313,7 +11390,7 @@
       <c r="AA104" s="10">
         <v>0</v>
       </c>
-      <c r="AB104" s="10"/>
+      <c r="AB104" s="19"/>
       <c r="AC104" s="10"/>
       <c r="AD104" s="1"/>
       <c r="AE104" s="1"/>
@@ -11339,7 +11416,7 @@
     </row>
     <row r="105" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>35</v>
@@ -11357,7 +11434,7 @@
       </c>
       <c r="H105" s="10"/>
       <c r="I105" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J105" s="10"/>
       <c r="K105" s="10"/>
@@ -11403,7 +11480,7 @@
       <c r="AA105" s="10">
         <v>0</v>
       </c>
-      <c r="AB105" s="10"/>
+      <c r="AB105" s="19"/>
       <c r="AC105" s="10"/>
       <c r="AD105" s="1"/>
       <c r="AE105" s="1"/>
@@ -11429,7 +11506,7 @@
     </row>
     <row r="106" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>33</v>
@@ -11447,7 +11524,7 @@
       </c>
       <c r="H106" s="10"/>
       <c r="I106" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J106" s="10" t="s">
         <v>104</v>
@@ -11497,7 +11574,7 @@
       <c r="AA106" s="10">
         <v>0</v>
       </c>
-      <c r="AB106" s="10"/>
+      <c r="AB106" s="19"/>
       <c r="AC106" s="10"/>
       <c r="AD106" s="1"/>
       <c r="AE106" s="1"/>
@@ -11549,7 +11626,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
-      <c r="AB107" s="1"/>
+      <c r="AB107" s="17"/>
       <c r="AC107" s="1"/>
       <c r="AD107" s="1"/>
       <c r="AE107" s="1"/>
@@ -11601,7 +11678,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
-      <c r="AB108" s="1"/>
+      <c r="AB108" s="17"/>
       <c r="AC108" s="1"/>
       <c r="AD108" s="1"/>
       <c r="AE108" s="1"/>
@@ -11653,7 +11730,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
-      <c r="AB109" s="1"/>
+      <c r="AB109" s="17"/>
       <c r="AC109" s="1"/>
       <c r="AD109" s="1"/>
       <c r="AE109" s="1"/>
@@ -11705,7 +11782,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
-      <c r="AB110" s="1"/>
+      <c r="AB110" s="17"/>
       <c r="AC110" s="1"/>
       <c r="AD110" s="1"/>
       <c r="AE110" s="1"/>
@@ -11757,7 +11834,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
       <c r="AA111" s="1"/>
-      <c r="AB111" s="1"/>
+      <c r="AB111" s="17"/>
       <c r="AC111" s="1"/>
       <c r="AD111" s="1"/>
       <c r="AE111" s="1"/>
@@ -11809,7 +11886,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
-      <c r="AB112" s="1"/>
+      <c r="AB112" s="17"/>
       <c r="AC112" s="1"/>
       <c r="AD112" s="1"/>
       <c r="AE112" s="1"/>
@@ -11861,7 +11938,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
-      <c r="AB113" s="1"/>
+      <c r="AB113" s="17"/>
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
       <c r="AE113" s="1"/>
@@ -11913,7 +11990,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
-      <c r="AB114" s="1"/>
+      <c r="AB114" s="17"/>
       <c r="AC114" s="1"/>
       <c r="AD114" s="1"/>
       <c r="AE114" s="1"/>
@@ -11965,7 +12042,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
-      <c r="AB115" s="1"/>
+      <c r="AB115" s="17"/>
       <c r="AC115" s="1"/>
       <c r="AD115" s="1"/>
       <c r="AE115" s="1"/>
@@ -12017,7 +12094,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
       <c r="AA116" s="1"/>
-      <c r="AB116" s="1"/>
+      <c r="AB116" s="17"/>
       <c r="AC116" s="1"/>
       <c r="AD116" s="1"/>
       <c r="AE116" s="1"/>
@@ -12069,7 +12146,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
-      <c r="AB117" s="1"/>
+      <c r="AB117" s="17"/>
       <c r="AC117" s="1"/>
       <c r="AD117" s="1"/>
       <c r="AE117" s="1"/>
@@ -12121,7 +12198,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
       <c r="AA118" s="1"/>
-      <c r="AB118" s="1"/>
+      <c r="AB118" s="17"/>
       <c r="AC118" s="1"/>
       <c r="AD118" s="1"/>
       <c r="AE118" s="1"/>
@@ -12173,7 +12250,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
       <c r="AA119" s="1"/>
-      <c r="AB119" s="1"/>
+      <c r="AB119" s="17"/>
       <c r="AC119" s="1"/>
       <c r="AD119" s="1"/>
       <c r="AE119" s="1"/>
@@ -12225,7 +12302,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
       <c r="AA120" s="1"/>
-      <c r="AB120" s="1"/>
+      <c r="AB120" s="17"/>
       <c r="AC120" s="1"/>
       <c r="AD120" s="1"/>
       <c r="AE120" s="1"/>
@@ -12277,7 +12354,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
-      <c r="AB121" s="1"/>
+      <c r="AB121" s="17"/>
       <c r="AC121" s="1"/>
       <c r="AD121" s="1"/>
       <c r="AE121" s="1"/>
@@ -12329,7 +12406,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
-      <c r="AB122" s="1"/>
+      <c r="AB122" s="17"/>
       <c r="AC122" s="1"/>
       <c r="AD122" s="1"/>
       <c r="AE122" s="1"/>
@@ -12381,7 +12458,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
-      <c r="AB123" s="1"/>
+      <c r="AB123" s="17"/>
       <c r="AC123" s="1"/>
       <c r="AD123" s="1"/>
       <c r="AE123" s="1"/>
@@ -12433,7 +12510,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
-      <c r="AB124" s="1"/>
+      <c r="AB124" s="17"/>
       <c r="AC124" s="1"/>
       <c r="AD124" s="1"/>
       <c r="AE124" s="1"/>
@@ -12485,7 +12562,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
       <c r="AA125" s="1"/>
-      <c r="AB125" s="1"/>
+      <c r="AB125" s="17"/>
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
       <c r="AE125" s="1"/>
@@ -12537,7 +12614,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
       <c r="AA126" s="1"/>
-      <c r="AB126" s="1"/>
+      <c r="AB126" s="17"/>
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
       <c r="AE126" s="1"/>
@@ -12589,7 +12666,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
       <c r="AA127" s="1"/>
-      <c r="AB127" s="1"/>
+      <c r="AB127" s="17"/>
       <c r="AC127" s="1"/>
       <c r="AD127" s="1"/>
       <c r="AE127" s="1"/>
@@ -12641,7 +12718,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
       <c r="AA128" s="1"/>
-      <c r="AB128" s="1"/>
+      <c r="AB128" s="17"/>
       <c r="AC128" s="1"/>
       <c r="AD128" s="1"/>
       <c r="AE128" s="1"/>
@@ -12693,7 +12770,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
       <c r="AA129" s="1"/>
-      <c r="AB129" s="1"/>
+      <c r="AB129" s="17"/>
       <c r="AC129" s="1"/>
       <c r="AD129" s="1"/>
       <c r="AE129" s="1"/>
@@ -12745,7 +12822,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
       <c r="AA130" s="1"/>
-      <c r="AB130" s="1"/>
+      <c r="AB130" s="17"/>
       <c r="AC130" s="1"/>
       <c r="AD130" s="1"/>
       <c r="AE130" s="1"/>
@@ -12797,7 +12874,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
       <c r="AA131" s="1"/>
-      <c r="AB131" s="1"/>
+      <c r="AB131" s="17"/>
       <c r="AC131" s="1"/>
       <c r="AD131" s="1"/>
       <c r="AE131" s="1"/>
@@ -12849,7 +12926,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
       <c r="AA132" s="1"/>
-      <c r="AB132" s="1"/>
+      <c r="AB132" s="17"/>
       <c r="AC132" s="1"/>
       <c r="AD132" s="1"/>
       <c r="AE132" s="1"/>
@@ -12901,7 +12978,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
       <c r="AA133" s="1"/>
-      <c r="AB133" s="1"/>
+      <c r="AB133" s="17"/>
       <c r="AC133" s="1"/>
       <c r="AD133" s="1"/>
       <c r="AE133" s="1"/>
@@ -12953,7 +13030,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
       <c r="AA134" s="1"/>
-      <c r="AB134" s="1"/>
+      <c r="AB134" s="17"/>
       <c r="AC134" s="1"/>
       <c r="AD134" s="1"/>
       <c r="AE134" s="1"/>
@@ -13005,7 +13082,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
       <c r="AA135" s="1"/>
-      <c r="AB135" s="1"/>
+      <c r="AB135" s="17"/>
       <c r="AC135" s="1"/>
       <c r="AD135" s="1"/>
       <c r="AE135" s="1"/>
@@ -13057,7 +13134,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
       <c r="AA136" s="1"/>
-      <c r="AB136" s="1"/>
+      <c r="AB136" s="17"/>
       <c r="AC136" s="1"/>
       <c r="AD136" s="1"/>
       <c r="AE136" s="1"/>
@@ -13109,7 +13186,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
       <c r="AA137" s="1"/>
-      <c r="AB137" s="1"/>
+      <c r="AB137" s="17"/>
       <c r="AC137" s="1"/>
       <c r="AD137" s="1"/>
       <c r="AE137" s="1"/>
@@ -13161,7 +13238,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
       <c r="AA138" s="1"/>
-      <c r="AB138" s="1"/>
+      <c r="AB138" s="17"/>
       <c r="AC138" s="1"/>
       <c r="AD138" s="1"/>
       <c r="AE138" s="1"/>
@@ -13213,7 +13290,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
       <c r="AA139" s="1"/>
-      <c r="AB139" s="1"/>
+      <c r="AB139" s="17"/>
       <c r="AC139" s="1"/>
       <c r="AD139" s="1"/>
       <c r="AE139" s="1"/>
@@ -13265,7 +13342,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
       <c r="AA140" s="1"/>
-      <c r="AB140" s="1"/>
+      <c r="AB140" s="17"/>
       <c r="AC140" s="1"/>
       <c r="AD140" s="1"/>
       <c r="AE140" s="1"/>
@@ -13317,7 +13394,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
       <c r="AA141" s="1"/>
-      <c r="AB141" s="1"/>
+      <c r="AB141" s="17"/>
       <c r="AC141" s="1"/>
       <c r="AD141" s="1"/>
       <c r="AE141" s="1"/>
@@ -13369,7 +13446,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
       <c r="AA142" s="1"/>
-      <c r="AB142" s="1"/>
+      <c r="AB142" s="17"/>
       <c r="AC142" s="1"/>
       <c r="AD142" s="1"/>
       <c r="AE142" s="1"/>
@@ -13421,7 +13498,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
       <c r="AA143" s="1"/>
-      <c r="AB143" s="1"/>
+      <c r="AB143" s="17"/>
       <c r="AC143" s="1"/>
       <c r="AD143" s="1"/>
       <c r="AE143" s="1"/>
@@ -13473,7 +13550,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
       <c r="AA144" s="1"/>
-      <c r="AB144" s="1"/>
+      <c r="AB144" s="17"/>
       <c r="AC144" s="1"/>
       <c r="AD144" s="1"/>
       <c r="AE144" s="1"/>
@@ -13525,7 +13602,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
       <c r="AA145" s="1"/>
-      <c r="AB145" s="1"/>
+      <c r="AB145" s="17"/>
       <c r="AC145" s="1"/>
       <c r="AD145" s="1"/>
       <c r="AE145" s="1"/>
@@ -13577,7 +13654,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
       <c r="AA146" s="1"/>
-      <c r="AB146" s="1"/>
+      <c r="AB146" s="17"/>
       <c r="AC146" s="1"/>
       <c r="AD146" s="1"/>
       <c r="AE146" s="1"/>
@@ -13629,7 +13706,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
       <c r="AA147" s="1"/>
-      <c r="AB147" s="1"/>
+      <c r="AB147" s="17"/>
       <c r="AC147" s="1"/>
       <c r="AD147" s="1"/>
       <c r="AE147" s="1"/>
@@ -13681,7 +13758,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
       <c r="AA148" s="1"/>
-      <c r="AB148" s="1"/>
+      <c r="AB148" s="17"/>
       <c r="AC148" s="1"/>
       <c r="AD148" s="1"/>
       <c r="AE148" s="1"/>
@@ -13733,7 +13810,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
       <c r="AA149" s="1"/>
-      <c r="AB149" s="1"/>
+      <c r="AB149" s="17"/>
       <c r="AC149" s="1"/>
       <c r="AD149" s="1"/>
       <c r="AE149" s="1"/>
@@ -13785,7 +13862,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
       <c r="AA150" s="1"/>
-      <c r="AB150" s="1"/>
+      <c r="AB150" s="17"/>
       <c r="AC150" s="1"/>
       <c r="AD150" s="1"/>
       <c r="AE150" s="1"/>
@@ -13837,7 +13914,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
       <c r="AA151" s="1"/>
-      <c r="AB151" s="1"/>
+      <c r="AB151" s="17"/>
       <c r="AC151" s="1"/>
       <c r="AD151" s="1"/>
       <c r="AE151" s="1"/>
@@ -13889,7 +13966,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
       <c r="AA152" s="1"/>
-      <c r="AB152" s="1"/>
+      <c r="AB152" s="17"/>
       <c r="AC152" s="1"/>
       <c r="AD152" s="1"/>
       <c r="AE152" s="1"/>
@@ -13941,7 +14018,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
       <c r="AA153" s="1"/>
-      <c r="AB153" s="1"/>
+      <c r="AB153" s="17"/>
       <c r="AC153" s="1"/>
       <c r="AD153" s="1"/>
       <c r="AE153" s="1"/>
@@ -13993,7 +14070,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
       <c r="AA154" s="1"/>
-      <c r="AB154" s="1"/>
+      <c r="AB154" s="17"/>
       <c r="AC154" s="1"/>
       <c r="AD154" s="1"/>
       <c r="AE154" s="1"/>
@@ -14045,7 +14122,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
       <c r="AA155" s="1"/>
-      <c r="AB155" s="1"/>
+      <c r="AB155" s="17"/>
       <c r="AC155" s="1"/>
       <c r="AD155" s="1"/>
       <c r="AE155" s="1"/>
@@ -14097,7 +14174,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
       <c r="AA156" s="1"/>
-      <c r="AB156" s="1"/>
+      <c r="AB156" s="17"/>
       <c r="AC156" s="1"/>
       <c r="AD156" s="1"/>
       <c r="AE156" s="1"/>
@@ -14149,7 +14226,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
       <c r="AA157" s="1"/>
-      <c r="AB157" s="1"/>
+      <c r="AB157" s="17"/>
       <c r="AC157" s="1"/>
       <c r="AD157" s="1"/>
       <c r="AE157" s="1"/>
@@ -14201,7 +14278,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
       <c r="AA158" s="1"/>
-      <c r="AB158" s="1"/>
+      <c r="AB158" s="17"/>
       <c r="AC158" s="1"/>
       <c r="AD158" s="1"/>
       <c r="AE158" s="1"/>
@@ -14253,7 +14330,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
       <c r="AA159" s="1"/>
-      <c r="AB159" s="1"/>
+      <c r="AB159" s="17"/>
       <c r="AC159" s="1"/>
       <c r="AD159" s="1"/>
       <c r="AE159" s="1"/>
@@ -14305,7 +14382,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
       <c r="AA160" s="1"/>
-      <c r="AB160" s="1"/>
+      <c r="AB160" s="17"/>
       <c r="AC160" s="1"/>
       <c r="AD160" s="1"/>
       <c r="AE160" s="1"/>
@@ -14357,7 +14434,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
       <c r="AA161" s="1"/>
-      <c r="AB161" s="1"/>
+      <c r="AB161" s="17"/>
       <c r="AC161" s="1"/>
       <c r="AD161" s="1"/>
       <c r="AE161" s="1"/>
@@ -14409,7 +14486,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
       <c r="AA162" s="1"/>
-      <c r="AB162" s="1"/>
+      <c r="AB162" s="17"/>
       <c r="AC162" s="1"/>
       <c r="AD162" s="1"/>
       <c r="AE162" s="1"/>
@@ -14461,7 +14538,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
       <c r="AA163" s="1"/>
-      <c r="AB163" s="1"/>
+      <c r="AB163" s="17"/>
       <c r="AC163" s="1"/>
       <c r="AD163" s="1"/>
       <c r="AE163" s="1"/>
@@ -14513,7 +14590,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
       <c r="AA164" s="1"/>
-      <c r="AB164" s="1"/>
+      <c r="AB164" s="17"/>
       <c r="AC164" s="1"/>
       <c r="AD164" s="1"/>
       <c r="AE164" s="1"/>
@@ -14565,7 +14642,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
       <c r="AA165" s="1"/>
-      <c r="AB165" s="1"/>
+      <c r="AB165" s="17"/>
       <c r="AC165" s="1"/>
       <c r="AD165" s="1"/>
       <c r="AE165" s="1"/>
@@ -14617,7 +14694,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
       <c r="AA166" s="1"/>
-      <c r="AB166" s="1"/>
+      <c r="AB166" s="17"/>
       <c r="AC166" s="1"/>
       <c r="AD166" s="1"/>
       <c r="AE166" s="1"/>
@@ -14669,7 +14746,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
       <c r="AA167" s="1"/>
-      <c r="AB167" s="1"/>
+      <c r="AB167" s="17"/>
       <c r="AC167" s="1"/>
       <c r="AD167" s="1"/>
       <c r="AE167" s="1"/>
@@ -14721,7 +14798,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
       <c r="AA168" s="1"/>
-      <c r="AB168" s="1"/>
+      <c r="AB168" s="17"/>
       <c r="AC168" s="1"/>
       <c r="AD168" s="1"/>
       <c r="AE168" s="1"/>
@@ -14773,7 +14850,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
       <c r="AA169" s="1"/>
-      <c r="AB169" s="1"/>
+      <c r="AB169" s="17"/>
       <c r="AC169" s="1"/>
       <c r="AD169" s="1"/>
       <c r="AE169" s="1"/>
@@ -14825,7 +14902,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
       <c r="AA170" s="1"/>
-      <c r="AB170" s="1"/>
+      <c r="AB170" s="17"/>
       <c r="AC170" s="1"/>
       <c r="AD170" s="1"/>
       <c r="AE170" s="1"/>
@@ -14877,7 +14954,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
       <c r="AA171" s="1"/>
-      <c r="AB171" s="1"/>
+      <c r="AB171" s="17"/>
       <c r="AC171" s="1"/>
       <c r="AD171" s="1"/>
       <c r="AE171" s="1"/>
@@ -14929,7 +15006,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
       <c r="AA172" s="1"/>
-      <c r="AB172" s="1"/>
+      <c r="AB172" s="17"/>
       <c r="AC172" s="1"/>
       <c r="AD172" s="1"/>
       <c r="AE172" s="1"/>
@@ -14981,7 +15058,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
       <c r="AA173" s="1"/>
-      <c r="AB173" s="1"/>
+      <c r="AB173" s="17"/>
       <c r="AC173" s="1"/>
       <c r="AD173" s="1"/>
       <c r="AE173" s="1"/>
@@ -15033,7 +15110,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
       <c r="AA174" s="1"/>
-      <c r="AB174" s="1"/>
+      <c r="AB174" s="17"/>
       <c r="AC174" s="1"/>
       <c r="AD174" s="1"/>
       <c r="AE174" s="1"/>
@@ -15085,7 +15162,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
       <c r="AA175" s="1"/>
-      <c r="AB175" s="1"/>
+      <c r="AB175" s="17"/>
       <c r="AC175" s="1"/>
       <c r="AD175" s="1"/>
       <c r="AE175" s="1"/>
@@ -15137,7 +15214,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
       <c r="AA176" s="1"/>
-      <c r="AB176" s="1"/>
+      <c r="AB176" s="17"/>
       <c r="AC176" s="1"/>
       <c r="AD176" s="1"/>
       <c r="AE176" s="1"/>
@@ -15189,7 +15266,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
       <c r="AA177" s="1"/>
-      <c r="AB177" s="1"/>
+      <c r="AB177" s="17"/>
       <c r="AC177" s="1"/>
       <c r="AD177" s="1"/>
       <c r="AE177" s="1"/>
@@ -15241,7 +15318,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
       <c r="AA178" s="1"/>
-      <c r="AB178" s="1"/>
+      <c r="AB178" s="17"/>
       <c r="AC178" s="1"/>
       <c r="AD178" s="1"/>
       <c r="AE178" s="1"/>
@@ -15293,7 +15370,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
       <c r="AA179" s="1"/>
-      <c r="AB179" s="1"/>
+      <c r="AB179" s="17"/>
       <c r="AC179" s="1"/>
       <c r="AD179" s="1"/>
       <c r="AE179" s="1"/>
@@ -15345,7 +15422,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
       <c r="AA180" s="1"/>
-      <c r="AB180" s="1"/>
+      <c r="AB180" s="17"/>
       <c r="AC180" s="1"/>
       <c r="AD180" s="1"/>
       <c r="AE180" s="1"/>
@@ -15397,7 +15474,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
       <c r="AA181" s="1"/>
-      <c r="AB181" s="1"/>
+      <c r="AB181" s="17"/>
       <c r="AC181" s="1"/>
       <c r="AD181" s="1"/>
       <c r="AE181" s="1"/>
@@ -15449,7 +15526,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
       <c r="AA182" s="1"/>
-      <c r="AB182" s="1"/>
+      <c r="AB182" s="17"/>
       <c r="AC182" s="1"/>
       <c r="AD182" s="1"/>
       <c r="AE182" s="1"/>
@@ -15501,7 +15578,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
       <c r="AA183" s="1"/>
-      <c r="AB183" s="1"/>
+      <c r="AB183" s="17"/>
       <c r="AC183" s="1"/>
       <c r="AD183" s="1"/>
       <c r="AE183" s="1"/>
@@ -15553,7 +15630,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
       <c r="AA184" s="1"/>
-      <c r="AB184" s="1"/>
+      <c r="AB184" s="17"/>
       <c r="AC184" s="1"/>
       <c r="AD184" s="1"/>
       <c r="AE184" s="1"/>
@@ -15605,7 +15682,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
       <c r="AA185" s="1"/>
-      <c r="AB185" s="1"/>
+      <c r="AB185" s="17"/>
       <c r="AC185" s="1"/>
       <c r="AD185" s="1"/>
       <c r="AE185" s="1"/>
@@ -15657,7 +15734,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
       <c r="AA186" s="1"/>
-      <c r="AB186" s="1"/>
+      <c r="AB186" s="17"/>
       <c r="AC186" s="1"/>
       <c r="AD186" s="1"/>
       <c r="AE186" s="1"/>
@@ -15709,7 +15786,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
       <c r="AA187" s="1"/>
-      <c r="AB187" s="1"/>
+      <c r="AB187" s="17"/>
       <c r="AC187" s="1"/>
       <c r="AD187" s="1"/>
       <c r="AE187" s="1"/>
@@ -15761,7 +15838,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
       <c r="AA188" s="1"/>
-      <c r="AB188" s="1"/>
+      <c r="AB188" s="17"/>
       <c r="AC188" s="1"/>
       <c r="AD188" s="1"/>
       <c r="AE188" s="1"/>
@@ -15813,7 +15890,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
       <c r="AA189" s="1"/>
-      <c r="AB189" s="1"/>
+      <c r="AB189" s="17"/>
       <c r="AC189" s="1"/>
       <c r="AD189" s="1"/>
       <c r="AE189" s="1"/>
@@ -15865,7 +15942,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
       <c r="AA190" s="1"/>
-      <c r="AB190" s="1"/>
+      <c r="AB190" s="17"/>
       <c r="AC190" s="1"/>
       <c r="AD190" s="1"/>
       <c r="AE190" s="1"/>
@@ -15917,7 +15994,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
       <c r="AA191" s="1"/>
-      <c r="AB191" s="1"/>
+      <c r="AB191" s="17"/>
       <c r="AC191" s="1"/>
       <c r="AD191" s="1"/>
       <c r="AE191" s="1"/>
@@ -15969,7 +16046,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
       <c r="AA192" s="1"/>
-      <c r="AB192" s="1"/>
+      <c r="AB192" s="17"/>
       <c r="AC192" s="1"/>
       <c r="AD192" s="1"/>
       <c r="AE192" s="1"/>
@@ -16021,7 +16098,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
       <c r="AA193" s="1"/>
-      <c r="AB193" s="1"/>
+      <c r="AB193" s="17"/>
       <c r="AC193" s="1"/>
       <c r="AD193" s="1"/>
       <c r="AE193" s="1"/>
@@ -16073,7 +16150,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
       <c r="AA194" s="1"/>
-      <c r="AB194" s="1"/>
+      <c r="AB194" s="17"/>
       <c r="AC194" s="1"/>
       <c r="AD194" s="1"/>
       <c r="AE194" s="1"/>
@@ -16125,7 +16202,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
       <c r="AA195" s="1"/>
-      <c r="AB195" s="1"/>
+      <c r="AB195" s="17"/>
       <c r="AC195" s="1"/>
       <c r="AD195" s="1"/>
       <c r="AE195" s="1"/>
@@ -16177,7 +16254,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
       <c r="AA196" s="1"/>
-      <c r="AB196" s="1"/>
+      <c r="AB196" s="17"/>
       <c r="AC196" s="1"/>
       <c r="AD196" s="1"/>
       <c r="AE196" s="1"/>
@@ -16229,7 +16306,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
       <c r="AA197" s="1"/>
-      <c r="AB197" s="1"/>
+      <c r="AB197" s="17"/>
       <c r="AC197" s="1"/>
       <c r="AD197" s="1"/>
       <c r="AE197" s="1"/>
@@ -16281,7 +16358,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
       <c r="AA198" s="1"/>
-      <c r="AB198" s="1"/>
+      <c r="AB198" s="17"/>
       <c r="AC198" s="1"/>
       <c r="AD198" s="1"/>
       <c r="AE198" s="1"/>
@@ -16333,7 +16410,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
       <c r="AA199" s="1"/>
-      <c r="AB199" s="1"/>
+      <c r="AB199" s="17"/>
       <c r="AC199" s="1"/>
       <c r="AD199" s="1"/>
       <c r="AE199" s="1"/>
@@ -16385,7 +16462,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
       <c r="AA200" s="1"/>
-      <c r="AB200" s="1"/>
+      <c r="AB200" s="17"/>
       <c r="AC200" s="1"/>
       <c r="AD200" s="1"/>
       <c r="AE200" s="1"/>
@@ -16437,7 +16514,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
       <c r="AA201" s="1"/>
-      <c r="AB201" s="1"/>
+      <c r="AB201" s="17"/>
       <c r="AC201" s="1"/>
       <c r="AD201" s="1"/>
       <c r="AE201" s="1"/>
@@ -16489,7 +16566,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
       <c r="AA202" s="1"/>
-      <c r="AB202" s="1"/>
+      <c r="AB202" s="17"/>
       <c r="AC202" s="1"/>
       <c r="AD202" s="1"/>
       <c r="AE202" s="1"/>
@@ -16541,7 +16618,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
       <c r="AA203" s="1"/>
-      <c r="AB203" s="1"/>
+      <c r="AB203" s="17"/>
       <c r="AC203" s="1"/>
       <c r="AD203" s="1"/>
       <c r="AE203" s="1"/>
@@ -16593,7 +16670,7 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
       <c r="AA204" s="1"/>
-      <c r="AB204" s="1"/>
+      <c r="AB204" s="17"/>
       <c r="AC204" s="1"/>
       <c r="AD204" s="1"/>
       <c r="AE204" s="1"/>
@@ -16645,7 +16722,7 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
       <c r="AA205" s="1"/>
-      <c r="AB205" s="1"/>
+      <c r="AB205" s="17"/>
       <c r="AC205" s="1"/>
       <c r="AD205" s="1"/>
       <c r="AE205" s="1"/>
@@ -16697,7 +16774,7 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
       <c r="AA206" s="1"/>
-      <c r="AB206" s="1"/>
+      <c r="AB206" s="17"/>
       <c r="AC206" s="1"/>
       <c r="AD206" s="1"/>
       <c r="AE206" s="1"/>
@@ -16749,7 +16826,7 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
       <c r="AA207" s="1"/>
-      <c r="AB207" s="1"/>
+      <c r="AB207" s="17"/>
       <c r="AC207" s="1"/>
       <c r="AD207" s="1"/>
       <c r="AE207" s="1"/>
@@ -16801,7 +16878,7 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
       <c r="AA208" s="1"/>
-      <c r="AB208" s="1"/>
+      <c r="AB208" s="17"/>
       <c r="AC208" s="1"/>
       <c r="AD208" s="1"/>
       <c r="AE208" s="1"/>
@@ -16853,7 +16930,7 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
       <c r="AA209" s="1"/>
-      <c r="AB209" s="1"/>
+      <c r="AB209" s="17"/>
       <c r="AC209" s="1"/>
       <c r="AD209" s="1"/>
       <c r="AE209" s="1"/>
@@ -16905,7 +16982,7 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
       <c r="AA210" s="1"/>
-      <c r="AB210" s="1"/>
+      <c r="AB210" s="17"/>
       <c r="AC210" s="1"/>
       <c r="AD210" s="1"/>
       <c r="AE210" s="1"/>
@@ -16957,7 +17034,7 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
       <c r="AA211" s="1"/>
-      <c r="AB211" s="1"/>
+      <c r="AB211" s="17"/>
       <c r="AC211" s="1"/>
       <c r="AD211" s="1"/>
       <c r="AE211" s="1"/>
@@ -17009,7 +17086,7 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
       <c r="AA212" s="1"/>
-      <c r="AB212" s="1"/>
+      <c r="AB212" s="17"/>
       <c r="AC212" s="1"/>
       <c r="AD212" s="1"/>
       <c r="AE212" s="1"/>
@@ -17061,7 +17138,7 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
       <c r="AA213" s="1"/>
-      <c r="AB213" s="1"/>
+      <c r="AB213" s="17"/>
       <c r="AC213" s="1"/>
       <c r="AD213" s="1"/>
       <c r="AE213" s="1"/>
@@ -17113,7 +17190,7 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
       <c r="AA214" s="1"/>
-      <c r="AB214" s="1"/>
+      <c r="AB214" s="17"/>
       <c r="AC214" s="1"/>
       <c r="AD214" s="1"/>
       <c r="AE214" s="1"/>
@@ -17165,7 +17242,7 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
       <c r="AA215" s="1"/>
-      <c r="AB215" s="1"/>
+      <c r="AB215" s="17"/>
       <c r="AC215" s="1"/>
       <c r="AD215" s="1"/>
       <c r="AE215" s="1"/>
@@ -17217,7 +17294,7 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
       <c r="AA216" s="1"/>
-      <c r="AB216" s="1"/>
+      <c r="AB216" s="17"/>
       <c r="AC216" s="1"/>
       <c r="AD216" s="1"/>
       <c r="AE216" s="1"/>
@@ -17269,7 +17346,7 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
       <c r="AA217" s="1"/>
-      <c r="AB217" s="1"/>
+      <c r="AB217" s="17"/>
       <c r="AC217" s="1"/>
       <c r="AD217" s="1"/>
       <c r="AE217" s="1"/>
@@ -17321,7 +17398,7 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
       <c r="AA218" s="1"/>
-      <c r="AB218" s="1"/>
+      <c r="AB218" s="17"/>
       <c r="AC218" s="1"/>
       <c r="AD218" s="1"/>
       <c r="AE218" s="1"/>
@@ -17373,7 +17450,7 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
       <c r="AA219" s="1"/>
-      <c r="AB219" s="1"/>
+      <c r="AB219" s="17"/>
       <c r="AC219" s="1"/>
       <c r="AD219" s="1"/>
       <c r="AE219" s="1"/>
@@ -17425,7 +17502,7 @@
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
       <c r="AA220" s="1"/>
-      <c r="AB220" s="1"/>
+      <c r="AB220" s="17"/>
       <c r="AC220" s="1"/>
       <c r="AD220" s="1"/>
       <c r="AE220" s="1"/>
@@ -17477,7 +17554,7 @@
       <c r="Y221" s="1"/>
       <c r="Z221" s="1"/>
       <c r="AA221" s="1"/>
-      <c r="AB221" s="1"/>
+      <c r="AB221" s="17"/>
       <c r="AC221" s="1"/>
       <c r="AD221" s="1"/>
       <c r="AE221" s="1"/>
@@ -17529,7 +17606,7 @@
       <c r="Y222" s="1"/>
       <c r="Z222" s="1"/>
       <c r="AA222" s="1"/>
-      <c r="AB222" s="1"/>
+      <c r="AB222" s="17"/>
       <c r="AC222" s="1"/>
       <c r="AD222" s="1"/>
       <c r="AE222" s="1"/>
@@ -17581,7 +17658,7 @@
       <c r="Y223" s="1"/>
       <c r="Z223" s="1"/>
       <c r="AA223" s="1"/>
-      <c r="AB223" s="1"/>
+      <c r="AB223" s="17"/>
       <c r="AC223" s="1"/>
       <c r="AD223" s="1"/>
       <c r="AE223" s="1"/>
@@ -17633,7 +17710,7 @@
       <c r="Y224" s="1"/>
       <c r="Z224" s="1"/>
       <c r="AA224" s="1"/>
-      <c r="AB224" s="1"/>
+      <c r="AB224" s="17"/>
       <c r="AC224" s="1"/>
       <c r="AD224" s="1"/>
       <c r="AE224" s="1"/>
@@ -17685,7 +17762,7 @@
       <c r="Y225" s="1"/>
       <c r="Z225" s="1"/>
       <c r="AA225" s="1"/>
-      <c r="AB225" s="1"/>
+      <c r="AB225" s="17"/>
       <c r="AC225" s="1"/>
       <c r="AD225" s="1"/>
       <c r="AE225" s="1"/>
@@ -17737,7 +17814,7 @@
       <c r="Y226" s="1"/>
       <c r="Z226" s="1"/>
       <c r="AA226" s="1"/>
-      <c r="AB226" s="1"/>
+      <c r="AB226" s="17"/>
       <c r="AC226" s="1"/>
       <c r="AD226" s="1"/>
       <c r="AE226" s="1"/>
@@ -17789,7 +17866,7 @@
       <c r="Y227" s="1"/>
       <c r="Z227" s="1"/>
       <c r="AA227" s="1"/>
-      <c r="AB227" s="1"/>
+      <c r="AB227" s="17"/>
       <c r="AC227" s="1"/>
       <c r="AD227" s="1"/>
       <c r="AE227" s="1"/>
@@ -17841,7 +17918,7 @@
       <c r="Y228" s="1"/>
       <c r="Z228" s="1"/>
       <c r="AA228" s="1"/>
-      <c r="AB228" s="1"/>
+      <c r="AB228" s="17"/>
       <c r="AC228" s="1"/>
       <c r="AD228" s="1"/>
       <c r="AE228" s="1"/>
@@ -17893,7 +17970,7 @@
       <c r="Y229" s="1"/>
       <c r="Z229" s="1"/>
       <c r="AA229" s="1"/>
-      <c r="AB229" s="1"/>
+      <c r="AB229" s="17"/>
       <c r="AC229" s="1"/>
       <c r="AD229" s="1"/>
       <c r="AE229" s="1"/>
@@ -17945,7 +18022,7 @@
       <c r="Y230" s="1"/>
       <c r="Z230" s="1"/>
       <c r="AA230" s="1"/>
-      <c r="AB230" s="1"/>
+      <c r="AB230" s="17"/>
       <c r="AC230" s="1"/>
       <c r="AD230" s="1"/>
       <c r="AE230" s="1"/>
@@ -17997,7 +18074,7 @@
       <c r="Y231" s="1"/>
       <c r="Z231" s="1"/>
       <c r="AA231" s="1"/>
-      <c r="AB231" s="1"/>
+      <c r="AB231" s="17"/>
       <c r="AC231" s="1"/>
       <c r="AD231" s="1"/>
       <c r="AE231" s="1"/>
@@ -18049,7 +18126,7 @@
       <c r="Y232" s="1"/>
       <c r="Z232" s="1"/>
       <c r="AA232" s="1"/>
-      <c r="AB232" s="1"/>
+      <c r="AB232" s="17"/>
       <c r="AC232" s="1"/>
       <c r="AD232" s="1"/>
       <c r="AE232" s="1"/>
@@ -18101,7 +18178,7 @@
       <c r="Y233" s="1"/>
       <c r="Z233" s="1"/>
       <c r="AA233" s="1"/>
-      <c r="AB233" s="1"/>
+      <c r="AB233" s="17"/>
       <c r="AC233" s="1"/>
       <c r="AD233" s="1"/>
       <c r="AE233" s="1"/>
@@ -18153,7 +18230,7 @@
       <c r="Y234" s="1"/>
       <c r="Z234" s="1"/>
       <c r="AA234" s="1"/>
-      <c r="AB234" s="1"/>
+      <c r="AB234" s="17"/>
       <c r="AC234" s="1"/>
       <c r="AD234" s="1"/>
       <c r="AE234" s="1"/>
@@ -18205,7 +18282,7 @@
       <c r="Y235" s="1"/>
       <c r="Z235" s="1"/>
       <c r="AA235" s="1"/>
-      <c r="AB235" s="1"/>
+      <c r="AB235" s="17"/>
       <c r="AC235" s="1"/>
       <c r="AD235" s="1"/>
       <c r="AE235" s="1"/>
@@ -18257,7 +18334,7 @@
       <c r="Y236" s="1"/>
       <c r="Z236" s="1"/>
       <c r="AA236" s="1"/>
-      <c r="AB236" s="1"/>
+      <c r="AB236" s="17"/>
       <c r="AC236" s="1"/>
       <c r="AD236" s="1"/>
       <c r="AE236" s="1"/>
@@ -18309,7 +18386,7 @@
       <c r="Y237" s="1"/>
       <c r="Z237" s="1"/>
       <c r="AA237" s="1"/>
-      <c r="AB237" s="1"/>
+      <c r="AB237" s="17"/>
       <c r="AC237" s="1"/>
       <c r="AD237" s="1"/>
       <c r="AE237" s="1"/>
@@ -18361,7 +18438,7 @@
       <c r="Y238" s="1"/>
       <c r="Z238" s="1"/>
       <c r="AA238" s="1"/>
-      <c r="AB238" s="1"/>
+      <c r="AB238" s="17"/>
       <c r="AC238" s="1"/>
       <c r="AD238" s="1"/>
       <c r="AE238" s="1"/>
@@ -18413,7 +18490,7 @@
       <c r="Y239" s="1"/>
       <c r="Z239" s="1"/>
       <c r="AA239" s="1"/>
-      <c r="AB239" s="1"/>
+      <c r="AB239" s="17"/>
       <c r="AC239" s="1"/>
       <c r="AD239" s="1"/>
       <c r="AE239" s="1"/>
@@ -18465,7 +18542,7 @@
       <c r="Y240" s="1"/>
       <c r="Z240" s="1"/>
       <c r="AA240" s="1"/>
-      <c r="AB240" s="1"/>
+      <c r="AB240" s="17"/>
       <c r="AC240" s="1"/>
       <c r="AD240" s="1"/>
       <c r="AE240" s="1"/>
@@ -18517,7 +18594,7 @@
       <c r="Y241" s="1"/>
       <c r="Z241" s="1"/>
       <c r="AA241" s="1"/>
-      <c r="AB241" s="1"/>
+      <c r="AB241" s="17"/>
       <c r="AC241" s="1"/>
       <c r="AD241" s="1"/>
       <c r="AE241" s="1"/>
@@ -18569,7 +18646,7 @@
       <c r="Y242" s="1"/>
       <c r="Z242" s="1"/>
       <c r="AA242" s="1"/>
-      <c r="AB242" s="1"/>
+      <c r="AB242" s="17"/>
       <c r="AC242" s="1"/>
       <c r="AD242" s="1"/>
       <c r="AE242" s="1"/>
@@ -18621,7 +18698,7 @@
       <c r="Y243" s="1"/>
       <c r="Z243" s="1"/>
       <c r="AA243" s="1"/>
-      <c r="AB243" s="1"/>
+      <c r="AB243" s="17"/>
       <c r="AC243" s="1"/>
       <c r="AD243" s="1"/>
       <c r="AE243" s="1"/>
@@ -18673,7 +18750,7 @@
       <c r="Y244" s="1"/>
       <c r="Z244" s="1"/>
       <c r="AA244" s="1"/>
-      <c r="AB244" s="1"/>
+      <c r="AB244" s="17"/>
       <c r="AC244" s="1"/>
       <c r="AD244" s="1"/>
       <c r="AE244" s="1"/>
@@ -18725,7 +18802,7 @@
       <c r="Y245" s="1"/>
       <c r="Z245" s="1"/>
       <c r="AA245" s="1"/>
-      <c r="AB245" s="1"/>
+      <c r="AB245" s="17"/>
       <c r="AC245" s="1"/>
       <c r="AD245" s="1"/>
       <c r="AE245" s="1"/>
@@ -18777,7 +18854,7 @@
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
       <c r="AA246" s="1"/>
-      <c r="AB246" s="1"/>
+      <c r="AB246" s="17"/>
       <c r="AC246" s="1"/>
       <c r="AD246" s="1"/>
       <c r="AE246" s="1"/>
@@ -18829,7 +18906,7 @@
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
       <c r="AA247" s="1"/>
-      <c r="AB247" s="1"/>
+      <c r="AB247" s="17"/>
       <c r="AC247" s="1"/>
       <c r="AD247" s="1"/>
       <c r="AE247" s="1"/>
@@ -18881,7 +18958,7 @@
       <c r="Y248" s="1"/>
       <c r="Z248" s="1"/>
       <c r="AA248" s="1"/>
-      <c r="AB248" s="1"/>
+      <c r="AB248" s="17"/>
       <c r="AC248" s="1"/>
       <c r="AD248" s="1"/>
       <c r="AE248" s="1"/>
@@ -18933,7 +19010,7 @@
       <c r="Y249" s="1"/>
       <c r="Z249" s="1"/>
       <c r="AA249" s="1"/>
-      <c r="AB249" s="1"/>
+      <c r="AB249" s="17"/>
       <c r="AC249" s="1"/>
       <c r="AD249" s="1"/>
       <c r="AE249" s="1"/>
@@ -18985,7 +19062,7 @@
       <c r="Y250" s="1"/>
       <c r="Z250" s="1"/>
       <c r="AA250" s="1"/>
-      <c r="AB250" s="1"/>
+      <c r="AB250" s="17"/>
       <c r="AC250" s="1"/>
       <c r="AD250" s="1"/>
       <c r="AE250" s="1"/>
@@ -19037,7 +19114,7 @@
       <c r="Y251" s="1"/>
       <c r="Z251" s="1"/>
       <c r="AA251" s="1"/>
-      <c r="AB251" s="1"/>
+      <c r="AB251" s="17"/>
       <c r="AC251" s="1"/>
       <c r="AD251" s="1"/>
       <c r="AE251" s="1"/>
@@ -19089,7 +19166,7 @@
       <c r="Y252" s="1"/>
       <c r="Z252" s="1"/>
       <c r="AA252" s="1"/>
-      <c r="AB252" s="1"/>
+      <c r="AB252" s="17"/>
       <c r="AC252" s="1"/>
       <c r="AD252" s="1"/>
       <c r="AE252" s="1"/>
@@ -19141,7 +19218,7 @@
       <c r="Y253" s="1"/>
       <c r="Z253" s="1"/>
       <c r="AA253" s="1"/>
-      <c r="AB253" s="1"/>
+      <c r="AB253" s="17"/>
       <c r="AC253" s="1"/>
       <c r="AD253" s="1"/>
       <c r="AE253" s="1"/>
@@ -19193,7 +19270,7 @@
       <c r="Y254" s="1"/>
       <c r="Z254" s="1"/>
       <c r="AA254" s="1"/>
-      <c r="AB254" s="1"/>
+      <c r="AB254" s="17"/>
       <c r="AC254" s="1"/>
       <c r="AD254" s="1"/>
       <c r="AE254" s="1"/>
@@ -19245,7 +19322,7 @@
       <c r="Y255" s="1"/>
       <c r="Z255" s="1"/>
       <c r="AA255" s="1"/>
-      <c r="AB255" s="1"/>
+      <c r="AB255" s="17"/>
       <c r="AC255" s="1"/>
       <c r="AD255" s="1"/>
       <c r="AE255" s="1"/>
@@ -19297,7 +19374,7 @@
       <c r="Y256" s="1"/>
       <c r="Z256" s="1"/>
       <c r="AA256" s="1"/>
-      <c r="AB256" s="1"/>
+      <c r="AB256" s="17"/>
       <c r="AC256" s="1"/>
       <c r="AD256" s="1"/>
       <c r="AE256" s="1"/>
@@ -19349,7 +19426,7 @@
       <c r="Y257" s="1"/>
       <c r="Z257" s="1"/>
       <c r="AA257" s="1"/>
-      <c r="AB257" s="1"/>
+      <c r="AB257" s="17"/>
       <c r="AC257" s="1"/>
       <c r="AD257" s="1"/>
       <c r="AE257" s="1"/>
@@ -19401,7 +19478,7 @@
       <c r="Y258" s="1"/>
       <c r="Z258" s="1"/>
       <c r="AA258" s="1"/>
-      <c r="AB258" s="1"/>
+      <c r="AB258" s="17"/>
       <c r="AC258" s="1"/>
       <c r="AD258" s="1"/>
       <c r="AE258" s="1"/>
@@ -19453,7 +19530,7 @@
       <c r="Y259" s="1"/>
       <c r="Z259" s="1"/>
       <c r="AA259" s="1"/>
-      <c r="AB259" s="1"/>
+      <c r="AB259" s="17"/>
       <c r="AC259" s="1"/>
       <c r="AD259" s="1"/>
       <c r="AE259" s="1"/>
@@ -19505,7 +19582,7 @@
       <c r="Y260" s="1"/>
       <c r="Z260" s="1"/>
       <c r="AA260" s="1"/>
-      <c r="AB260" s="1"/>
+      <c r="AB260" s="17"/>
       <c r="AC260" s="1"/>
       <c r="AD260" s="1"/>
       <c r="AE260" s="1"/>
@@ -19557,7 +19634,7 @@
       <c r="Y261" s="1"/>
       <c r="Z261" s="1"/>
       <c r="AA261" s="1"/>
-      <c r="AB261" s="1"/>
+      <c r="AB261" s="17"/>
       <c r="AC261" s="1"/>
       <c r="AD261" s="1"/>
       <c r="AE261" s="1"/>
@@ -19609,7 +19686,7 @@
       <c r="Y262" s="1"/>
       <c r="Z262" s="1"/>
       <c r="AA262" s="1"/>
-      <c r="AB262" s="1"/>
+      <c r="AB262" s="17"/>
       <c r="AC262" s="1"/>
       <c r="AD262" s="1"/>
       <c r="AE262" s="1"/>
@@ -19661,7 +19738,7 @@
       <c r="Y263" s="1"/>
       <c r="Z263" s="1"/>
       <c r="AA263" s="1"/>
-      <c r="AB263" s="1"/>
+      <c r="AB263" s="17"/>
       <c r="AC263" s="1"/>
       <c r="AD263" s="1"/>
       <c r="AE263" s="1"/>
@@ -19713,7 +19790,7 @@
       <c r="Y264" s="1"/>
       <c r="Z264" s="1"/>
       <c r="AA264" s="1"/>
-      <c r="AB264" s="1"/>
+      <c r="AB264" s="17"/>
       <c r="AC264" s="1"/>
       <c r="AD264" s="1"/>
       <c r="AE264" s="1"/>
@@ -19765,7 +19842,7 @@
       <c r="Y265" s="1"/>
       <c r="Z265" s="1"/>
       <c r="AA265" s="1"/>
-      <c r="AB265" s="1"/>
+      <c r="AB265" s="17"/>
       <c r="AC265" s="1"/>
       <c r="AD265" s="1"/>
       <c r="AE265" s="1"/>
@@ -19817,7 +19894,7 @@
       <c r="Y266" s="1"/>
       <c r="Z266" s="1"/>
       <c r="AA266" s="1"/>
-      <c r="AB266" s="1"/>
+      <c r="AB266" s="17"/>
       <c r="AC266" s="1"/>
       <c r="AD266" s="1"/>
       <c r="AE266" s="1"/>
@@ -19869,7 +19946,7 @@
       <c r="Y267" s="1"/>
       <c r="Z267" s="1"/>
       <c r="AA267" s="1"/>
-      <c r="AB267" s="1"/>
+      <c r="AB267" s="17"/>
       <c r="AC267" s="1"/>
       <c r="AD267" s="1"/>
       <c r="AE267" s="1"/>
@@ -19921,7 +19998,7 @@
       <c r="Y268" s="1"/>
       <c r="Z268" s="1"/>
       <c r="AA268" s="1"/>
-      <c r="AB268" s="1"/>
+      <c r="AB268" s="17"/>
       <c r="AC268" s="1"/>
       <c r="AD268" s="1"/>
       <c r="AE268" s="1"/>
@@ -19973,7 +20050,7 @@
       <c r="Y269" s="1"/>
       <c r="Z269" s="1"/>
       <c r="AA269" s="1"/>
-      <c r="AB269" s="1"/>
+      <c r="AB269" s="17"/>
       <c r="AC269" s="1"/>
       <c r="AD269" s="1"/>
       <c r="AE269" s="1"/>
@@ -20025,7 +20102,7 @@
       <c r="Y270" s="1"/>
       <c r="Z270" s="1"/>
       <c r="AA270" s="1"/>
-      <c r="AB270" s="1"/>
+      <c r="AB270" s="17"/>
       <c r="AC270" s="1"/>
       <c r="AD270" s="1"/>
       <c r="AE270" s="1"/>
@@ -20077,7 +20154,7 @@
       <c r="Y271" s="1"/>
       <c r="Z271" s="1"/>
       <c r="AA271" s="1"/>
-      <c r="AB271" s="1"/>
+      <c r="AB271" s="17"/>
       <c r="AC271" s="1"/>
       <c r="AD271" s="1"/>
       <c r="AE271" s="1"/>
@@ -20129,7 +20206,7 @@
       <c r="Y272" s="1"/>
       <c r="Z272" s="1"/>
       <c r="AA272" s="1"/>
-      <c r="AB272" s="1"/>
+      <c r="AB272" s="17"/>
       <c r="AC272" s="1"/>
       <c r="AD272" s="1"/>
       <c r="AE272" s="1"/>
@@ -20181,7 +20258,7 @@
       <c r="Y273" s="1"/>
       <c r="Z273" s="1"/>
       <c r="AA273" s="1"/>
-      <c r="AB273" s="1"/>
+      <c r="AB273" s="17"/>
       <c r="AC273" s="1"/>
       <c r="AD273" s="1"/>
       <c r="AE273" s="1"/>
@@ -20233,7 +20310,7 @@
       <c r="Y274" s="1"/>
       <c r="Z274" s="1"/>
       <c r="AA274" s="1"/>
-      <c r="AB274" s="1"/>
+      <c r="AB274" s="17"/>
       <c r="AC274" s="1"/>
       <c r="AD274" s="1"/>
       <c r="AE274" s="1"/>
@@ -20285,7 +20362,7 @@
       <c r="Y275" s="1"/>
       <c r="Z275" s="1"/>
       <c r="AA275" s="1"/>
-      <c r="AB275" s="1"/>
+      <c r="AB275" s="17"/>
       <c r="AC275" s="1"/>
       <c r="AD275" s="1"/>
       <c r="AE275" s="1"/>
@@ -20337,7 +20414,7 @@
       <c r="Y276" s="1"/>
       <c r="Z276" s="1"/>
       <c r="AA276" s="1"/>
-      <c r="AB276" s="1"/>
+      <c r="AB276" s="17"/>
       <c r="AC276" s="1"/>
       <c r="AD276" s="1"/>
       <c r="AE276" s="1"/>
@@ -20389,7 +20466,7 @@
       <c r="Y277" s="1"/>
       <c r="Z277" s="1"/>
       <c r="AA277" s="1"/>
-      <c r="AB277" s="1"/>
+      <c r="AB277" s="17"/>
       <c r="AC277" s="1"/>
       <c r="AD277" s="1"/>
       <c r="AE277" s="1"/>
@@ -20441,7 +20518,7 @@
       <c r="Y278" s="1"/>
       <c r="Z278" s="1"/>
       <c r="AA278" s="1"/>
-      <c r="AB278" s="1"/>
+      <c r="AB278" s="17"/>
       <c r="AC278" s="1"/>
       <c r="AD278" s="1"/>
       <c r="AE278" s="1"/>
@@ -20493,7 +20570,7 @@
       <c r="Y279" s="1"/>
       <c r="Z279" s="1"/>
       <c r="AA279" s="1"/>
-      <c r="AB279" s="1"/>
+      <c r="AB279" s="17"/>
       <c r="AC279" s="1"/>
       <c r="AD279" s="1"/>
       <c r="AE279" s="1"/>
@@ -20545,7 +20622,7 @@
       <c r="Y280" s="1"/>
       <c r="Z280" s="1"/>
       <c r="AA280" s="1"/>
-      <c r="AB280" s="1"/>
+      <c r="AB280" s="17"/>
       <c r="AC280" s="1"/>
       <c r="AD280" s="1"/>
       <c r="AE280" s="1"/>
@@ -20597,7 +20674,7 @@
       <c r="Y281" s="1"/>
       <c r="Z281" s="1"/>
       <c r="AA281" s="1"/>
-      <c r="AB281" s="1"/>
+      <c r="AB281" s="17"/>
       <c r="AC281" s="1"/>
       <c r="AD281" s="1"/>
       <c r="AE281" s="1"/>
@@ -20649,7 +20726,7 @@
       <c r="Y282" s="1"/>
       <c r="Z282" s="1"/>
       <c r="AA282" s="1"/>
-      <c r="AB282" s="1"/>
+      <c r="AB282" s="17"/>
       <c r="AC282" s="1"/>
       <c r="AD282" s="1"/>
       <c r="AE282" s="1"/>
@@ -20701,7 +20778,7 @@
       <c r="Y283" s="1"/>
       <c r="Z283" s="1"/>
       <c r="AA283" s="1"/>
-      <c r="AB283" s="1"/>
+      <c r="AB283" s="17"/>
       <c r="AC283" s="1"/>
       <c r="AD283" s="1"/>
       <c r="AE283" s="1"/>
@@ -20753,7 +20830,7 @@
       <c r="Y284" s="1"/>
       <c r="Z284" s="1"/>
       <c r="AA284" s="1"/>
-      <c r="AB284" s="1"/>
+      <c r="AB284" s="17"/>
       <c r="AC284" s="1"/>
       <c r="AD284" s="1"/>
       <c r="AE284" s="1"/>
@@ -20805,7 +20882,7 @@
       <c r="Y285" s="1"/>
       <c r="Z285" s="1"/>
       <c r="AA285" s="1"/>
-      <c r="AB285" s="1"/>
+      <c r="AB285" s="17"/>
       <c r="AC285" s="1"/>
       <c r="AD285" s="1"/>
       <c r="AE285" s="1"/>
@@ -20857,7 +20934,7 @@
       <c r="Y286" s="1"/>
       <c r="Z286" s="1"/>
       <c r="AA286" s="1"/>
-      <c r="AB286" s="1"/>
+      <c r="AB286" s="17"/>
       <c r="AC286" s="1"/>
       <c r="AD286" s="1"/>
       <c r="AE286" s="1"/>
@@ -20909,7 +20986,7 @@
       <c r="Y287" s="1"/>
       <c r="Z287" s="1"/>
       <c r="AA287" s="1"/>
-      <c r="AB287" s="1"/>
+      <c r="AB287" s="17"/>
       <c r="AC287" s="1"/>
       <c r="AD287" s="1"/>
       <c r="AE287" s="1"/>
@@ -20961,7 +21038,7 @@
       <c r="Y288" s="1"/>
       <c r="Z288" s="1"/>
       <c r="AA288" s="1"/>
-      <c r="AB288" s="1"/>
+      <c r="AB288" s="17"/>
       <c r="AC288" s="1"/>
       <c r="AD288" s="1"/>
       <c r="AE288" s="1"/>
@@ -21013,7 +21090,7 @@
       <c r="Y289" s="1"/>
       <c r="Z289" s="1"/>
       <c r="AA289" s="1"/>
-      <c r="AB289" s="1"/>
+      <c r="AB289" s="17"/>
       <c r="AC289" s="1"/>
       <c r="AD289" s="1"/>
       <c r="AE289" s="1"/>
@@ -21065,7 +21142,7 @@
       <c r="Y290" s="1"/>
       <c r="Z290" s="1"/>
       <c r="AA290" s="1"/>
-      <c r="AB290" s="1"/>
+      <c r="AB290" s="17"/>
       <c r="AC290" s="1"/>
       <c r="AD290" s="1"/>
       <c r="AE290" s="1"/>
@@ -21117,7 +21194,7 @@
       <c r="Y291" s="1"/>
       <c r="Z291" s="1"/>
       <c r="AA291" s="1"/>
-      <c r="AB291" s="1"/>
+      <c r="AB291" s="17"/>
       <c r="AC291" s="1"/>
       <c r="AD291" s="1"/>
       <c r="AE291" s="1"/>
@@ -21169,7 +21246,7 @@
       <c r="Y292" s="1"/>
       <c r="Z292" s="1"/>
       <c r="AA292" s="1"/>
-      <c r="AB292" s="1"/>
+      <c r="AB292" s="17"/>
       <c r="AC292" s="1"/>
       <c r="AD292" s="1"/>
       <c r="AE292" s="1"/>
@@ -21221,7 +21298,7 @@
       <c r="Y293" s="1"/>
       <c r="Z293" s="1"/>
       <c r="AA293" s="1"/>
-      <c r="AB293" s="1"/>
+      <c r="AB293" s="17"/>
       <c r="AC293" s="1"/>
       <c r="AD293" s="1"/>
       <c r="AE293" s="1"/>
@@ -21273,7 +21350,7 @@
       <c r="Y294" s="1"/>
       <c r="Z294" s="1"/>
       <c r="AA294" s="1"/>
-      <c r="AB294" s="1"/>
+      <c r="AB294" s="17"/>
       <c r="AC294" s="1"/>
       <c r="AD294" s="1"/>
       <c r="AE294" s="1"/>
@@ -21325,7 +21402,7 @@
       <c r="Y295" s="1"/>
       <c r="Z295" s="1"/>
       <c r="AA295" s="1"/>
-      <c r="AB295" s="1"/>
+      <c r="AB295" s="17"/>
       <c r="AC295" s="1"/>
       <c r="AD295" s="1"/>
       <c r="AE295" s="1"/>
@@ -21377,7 +21454,7 @@
       <c r="Y296" s="1"/>
       <c r="Z296" s="1"/>
       <c r="AA296" s="1"/>
-      <c r="AB296" s="1"/>
+      <c r="AB296" s="17"/>
       <c r="AC296" s="1"/>
       <c r="AD296" s="1"/>
       <c r="AE296" s="1"/>
@@ -21429,7 +21506,7 @@
       <c r="Y297" s="1"/>
       <c r="Z297" s="1"/>
       <c r="AA297" s="1"/>
-      <c r="AB297" s="1"/>
+      <c r="AB297" s="17"/>
       <c r="AC297" s="1"/>
       <c r="AD297" s="1"/>
       <c r="AE297" s="1"/>
@@ -21481,7 +21558,7 @@
       <c r="Y298" s="1"/>
       <c r="Z298" s="1"/>
       <c r="AA298" s="1"/>
-      <c r="AB298" s="1"/>
+      <c r="AB298" s="17"/>
       <c r="AC298" s="1"/>
       <c r="AD298" s="1"/>
       <c r="AE298" s="1"/>
@@ -21533,7 +21610,7 @@
       <c r="Y299" s="1"/>
       <c r="Z299" s="1"/>
       <c r="AA299" s="1"/>
-      <c r="AB299" s="1"/>
+      <c r="AB299" s="17"/>
       <c r="AC299" s="1"/>
       <c r="AD299" s="1"/>
       <c r="AE299" s="1"/>
@@ -21585,7 +21662,7 @@
       <c r="Y300" s="1"/>
       <c r="Z300" s="1"/>
       <c r="AA300" s="1"/>
-      <c r="AB300" s="1"/>
+      <c r="AB300" s="17"/>
       <c r="AC300" s="1"/>
       <c r="AD300" s="1"/>
       <c r="AE300" s="1"/>
@@ -21637,7 +21714,7 @@
       <c r="Y301" s="1"/>
       <c r="Z301" s="1"/>
       <c r="AA301" s="1"/>
-      <c r="AB301" s="1"/>
+      <c r="AB301" s="17"/>
       <c r="AC301" s="1"/>
       <c r="AD301" s="1"/>
       <c r="AE301" s="1"/>
@@ -21689,7 +21766,7 @@
       <c r="Y302" s="1"/>
       <c r="Z302" s="1"/>
       <c r="AA302" s="1"/>
-      <c r="AB302" s="1"/>
+      <c r="AB302" s="17"/>
       <c r="AC302" s="1"/>
       <c r="AD302" s="1"/>
       <c r="AE302" s="1"/>
@@ -21741,7 +21818,7 @@
       <c r="Y303" s="1"/>
       <c r="Z303" s="1"/>
       <c r="AA303" s="1"/>
-      <c r="AB303" s="1"/>
+      <c r="AB303" s="17"/>
       <c r="AC303" s="1"/>
       <c r="AD303" s="1"/>
       <c r="AE303" s="1"/>
@@ -21793,7 +21870,7 @@
       <c r="Y304" s="1"/>
       <c r="Z304" s="1"/>
       <c r="AA304" s="1"/>
-      <c r="AB304" s="1"/>
+      <c r="AB304" s="17"/>
       <c r="AC304" s="1"/>
       <c r="AD304" s="1"/>
       <c r="AE304" s="1"/>
@@ -21845,7 +21922,7 @@
       <c r="Y305" s="1"/>
       <c r="Z305" s="1"/>
       <c r="AA305" s="1"/>
-      <c r="AB305" s="1"/>
+      <c r="AB305" s="17"/>
       <c r="AC305" s="1"/>
       <c r="AD305" s="1"/>
       <c r="AE305" s="1"/>
@@ -21897,7 +21974,7 @@
       <c r="Y306" s="1"/>
       <c r="Z306" s="1"/>
       <c r="AA306" s="1"/>
-      <c r="AB306" s="1"/>
+      <c r="AB306" s="17"/>
       <c r="AC306" s="1"/>
       <c r="AD306" s="1"/>
       <c r="AE306" s="1"/>
@@ -21949,7 +22026,7 @@
       <c r="Y307" s="1"/>
       <c r="Z307" s="1"/>
       <c r="AA307" s="1"/>
-      <c r="AB307" s="1"/>
+      <c r="AB307" s="17"/>
       <c r="AC307" s="1"/>
       <c r="AD307" s="1"/>
       <c r="AE307" s="1"/>
@@ -22001,7 +22078,7 @@
       <c r="Y308" s="1"/>
       <c r="Z308" s="1"/>
       <c r="AA308" s="1"/>
-      <c r="AB308" s="1"/>
+      <c r="AB308" s="17"/>
       <c r="AC308" s="1"/>
       <c r="AD308" s="1"/>
       <c r="AE308" s="1"/>
@@ -22053,7 +22130,7 @@
       <c r="Y309" s="1"/>
       <c r="Z309" s="1"/>
       <c r="AA309" s="1"/>
-      <c r="AB309" s="1"/>
+      <c r="AB309" s="17"/>
       <c r="AC309" s="1"/>
       <c r="AD309" s="1"/>
       <c r="AE309" s="1"/>
@@ -22105,7 +22182,7 @@
       <c r="Y310" s="1"/>
       <c r="Z310" s="1"/>
       <c r="AA310" s="1"/>
-      <c r="AB310" s="1"/>
+      <c r="AB310" s="17"/>
       <c r="AC310" s="1"/>
       <c r="AD310" s="1"/>
       <c r="AE310" s="1"/>
@@ -22157,7 +22234,7 @@
       <c r="Y311" s="1"/>
       <c r="Z311" s="1"/>
       <c r="AA311" s="1"/>
-      <c r="AB311" s="1"/>
+      <c r="AB311" s="17"/>
       <c r="AC311" s="1"/>
       <c r="AD311" s="1"/>
       <c r="AE311" s="1"/>
@@ -22209,7 +22286,7 @@
       <c r="Y312" s="1"/>
       <c r="Z312" s="1"/>
       <c r="AA312" s="1"/>
-      <c r="AB312" s="1"/>
+      <c r="AB312" s="17"/>
       <c r="AC312" s="1"/>
       <c r="AD312" s="1"/>
       <c r="AE312" s="1"/>
@@ -22261,7 +22338,7 @@
       <c r="Y313" s="1"/>
       <c r="Z313" s="1"/>
       <c r="AA313" s="1"/>
-      <c r="AB313" s="1"/>
+      <c r="AB313" s="17"/>
       <c r="AC313" s="1"/>
       <c r="AD313" s="1"/>
       <c r="AE313" s="1"/>
@@ -22313,7 +22390,7 @@
       <c r="Y314" s="1"/>
       <c r="Z314" s="1"/>
       <c r="AA314" s="1"/>
-      <c r="AB314" s="1"/>
+      <c r="AB314" s="17"/>
       <c r="AC314" s="1"/>
       <c r="AD314" s="1"/>
       <c r="AE314" s="1"/>
@@ -22365,7 +22442,7 @@
       <c r="Y315" s="1"/>
       <c r="Z315" s="1"/>
       <c r="AA315" s="1"/>
-      <c r="AB315" s="1"/>
+      <c r="AB315" s="17"/>
       <c r="AC315" s="1"/>
       <c r="AD315" s="1"/>
       <c r="AE315" s="1"/>
@@ -22417,7 +22494,7 @@
       <c r="Y316" s="1"/>
       <c r="Z316" s="1"/>
       <c r="AA316" s="1"/>
-      <c r="AB316" s="1"/>
+      <c r="AB316" s="17"/>
       <c r="AC316" s="1"/>
       <c r="AD316" s="1"/>
       <c r="AE316" s="1"/>
@@ -22469,7 +22546,7 @@
       <c r="Y317" s="1"/>
       <c r="Z317" s="1"/>
       <c r="AA317" s="1"/>
-      <c r="AB317" s="1"/>
+      <c r="AB317" s="17"/>
       <c r="AC317" s="1"/>
       <c r="AD317" s="1"/>
       <c r="AE317" s="1"/>
@@ -22521,7 +22598,7 @@
       <c r="Y318" s="1"/>
       <c r="Z318" s="1"/>
       <c r="AA318" s="1"/>
-      <c r="AB318" s="1"/>
+      <c r="AB318" s="17"/>
       <c r="AC318" s="1"/>
       <c r="AD318" s="1"/>
       <c r="AE318" s="1"/>
@@ -22573,7 +22650,7 @@
       <c r="Y319" s="1"/>
       <c r="Z319" s="1"/>
       <c r="AA319" s="1"/>
-      <c r="AB319" s="1"/>
+      <c r="AB319" s="17"/>
       <c r="AC319" s="1"/>
       <c r="AD319" s="1"/>
       <c r="AE319" s="1"/>
@@ -22625,7 +22702,7 @@
       <c r="Y320" s="1"/>
       <c r="Z320" s="1"/>
       <c r="AA320" s="1"/>
-      <c r="AB320" s="1"/>
+      <c r="AB320" s="17"/>
       <c r="AC320" s="1"/>
       <c r="AD320" s="1"/>
       <c r="AE320" s="1"/>
@@ -22677,7 +22754,7 @@
       <c r="Y321" s="1"/>
       <c r="Z321" s="1"/>
       <c r="AA321" s="1"/>
-      <c r="AB321" s="1"/>
+      <c r="AB321" s="17"/>
       <c r="AC321" s="1"/>
       <c r="AD321" s="1"/>
       <c r="AE321" s="1"/>
@@ -22729,7 +22806,7 @@
       <c r="Y322" s="1"/>
       <c r="Z322" s="1"/>
       <c r="AA322" s="1"/>
-      <c r="AB322" s="1"/>
+      <c r="AB322" s="17"/>
       <c r="AC322" s="1"/>
       <c r="AD322" s="1"/>
       <c r="AE322" s="1"/>
@@ -22781,7 +22858,7 @@
       <c r="Y323" s="1"/>
       <c r="Z323" s="1"/>
       <c r="AA323" s="1"/>
-      <c r="AB323" s="1"/>
+      <c r="AB323" s="17"/>
       <c r="AC323" s="1"/>
       <c r="AD323" s="1"/>
       <c r="AE323" s="1"/>
@@ -22833,7 +22910,7 @@
       <c r="Y324" s="1"/>
       <c r="Z324" s="1"/>
       <c r="AA324" s="1"/>
-      <c r="AB324" s="1"/>
+      <c r="AB324" s="17"/>
       <c r="AC324" s="1"/>
       <c r="AD324" s="1"/>
       <c r="AE324" s="1"/>
@@ -22885,7 +22962,7 @@
       <c r="Y325" s="1"/>
       <c r="Z325" s="1"/>
       <c r="AA325" s="1"/>
-      <c r="AB325" s="1"/>
+      <c r="AB325" s="17"/>
       <c r="AC325" s="1"/>
       <c r="AD325" s="1"/>
       <c r="AE325" s="1"/>
@@ -22937,7 +23014,7 @@
       <c r="Y326" s="1"/>
       <c r="Z326" s="1"/>
       <c r="AA326" s="1"/>
-      <c r="AB326" s="1"/>
+      <c r="AB326" s="17"/>
       <c r="AC326" s="1"/>
       <c r="AD326" s="1"/>
       <c r="AE326" s="1"/>
@@ -22989,7 +23066,7 @@
       <c r="Y327" s="1"/>
       <c r="Z327" s="1"/>
       <c r="AA327" s="1"/>
-      <c r="AB327" s="1"/>
+      <c r="AB327" s="17"/>
       <c r="AC327" s="1"/>
       <c r="AD327" s="1"/>
       <c r="AE327" s="1"/>
@@ -23041,7 +23118,7 @@
       <c r="Y328" s="1"/>
       <c r="Z328" s="1"/>
       <c r="AA328" s="1"/>
-      <c r="AB328" s="1"/>
+      <c r="AB328" s="17"/>
       <c r="AC328" s="1"/>
       <c r="AD328" s="1"/>
       <c r="AE328" s="1"/>
@@ -23093,7 +23170,7 @@
       <c r="Y329" s="1"/>
       <c r="Z329" s="1"/>
       <c r="AA329" s="1"/>
-      <c r="AB329" s="1"/>
+      <c r="AB329" s="17"/>
       <c r="AC329" s="1"/>
       <c r="AD329" s="1"/>
       <c r="AE329" s="1"/>
@@ -23145,7 +23222,7 @@
       <c r="Y330" s="1"/>
       <c r="Z330" s="1"/>
       <c r="AA330" s="1"/>
-      <c r="AB330" s="1"/>
+      <c r="AB330" s="17"/>
       <c r="AC330" s="1"/>
       <c r="AD330" s="1"/>
       <c r="AE330" s="1"/>
@@ -23197,7 +23274,7 @@
       <c r="Y331" s="1"/>
       <c r="Z331" s="1"/>
       <c r="AA331" s="1"/>
-      <c r="AB331" s="1"/>
+      <c r="AB331" s="17"/>
       <c r="AC331" s="1"/>
       <c r="AD331" s="1"/>
       <c r="AE331" s="1"/>
@@ -23249,7 +23326,7 @@
       <c r="Y332" s="1"/>
       <c r="Z332" s="1"/>
       <c r="AA332" s="1"/>
-      <c r="AB332" s="1"/>
+      <c r="AB332" s="17"/>
       <c r="AC332" s="1"/>
       <c r="AD332" s="1"/>
       <c r="AE332" s="1"/>
@@ -23301,7 +23378,7 @@
       <c r="Y333" s="1"/>
       <c r="Z333" s="1"/>
       <c r="AA333" s="1"/>
-      <c r="AB333" s="1"/>
+      <c r="AB333" s="17"/>
       <c r="AC333" s="1"/>
       <c r="AD333" s="1"/>
       <c r="AE333" s="1"/>
@@ -23353,7 +23430,7 @@
       <c r="Y334" s="1"/>
       <c r="Z334" s="1"/>
       <c r="AA334" s="1"/>
-      <c r="AB334" s="1"/>
+      <c r="AB334" s="17"/>
       <c r="AC334" s="1"/>
       <c r="AD334" s="1"/>
       <c r="AE334" s="1"/>
@@ -23405,7 +23482,7 @@
       <c r="Y335" s="1"/>
       <c r="Z335" s="1"/>
       <c r="AA335" s="1"/>
-      <c r="AB335" s="1"/>
+      <c r="AB335" s="17"/>
       <c r="AC335" s="1"/>
       <c r="AD335" s="1"/>
       <c r="AE335" s="1"/>
@@ -23457,7 +23534,7 @@
       <c r="Y336" s="1"/>
       <c r="Z336" s="1"/>
       <c r="AA336" s="1"/>
-      <c r="AB336" s="1"/>
+      <c r="AB336" s="17"/>
       <c r="AC336" s="1"/>
       <c r="AD336" s="1"/>
       <c r="AE336" s="1"/>
@@ -23509,7 +23586,7 @@
       <c r="Y337" s="1"/>
       <c r="Z337" s="1"/>
       <c r="AA337" s="1"/>
-      <c r="AB337" s="1"/>
+      <c r="AB337" s="17"/>
       <c r="AC337" s="1"/>
       <c r="AD337" s="1"/>
       <c r="AE337" s="1"/>
@@ -23561,7 +23638,7 @@
       <c r="Y338" s="1"/>
       <c r="Z338" s="1"/>
       <c r="AA338" s="1"/>
-      <c r="AB338" s="1"/>
+      <c r="AB338" s="17"/>
       <c r="AC338" s="1"/>
       <c r="AD338" s="1"/>
       <c r="AE338" s="1"/>
@@ -23613,7 +23690,7 @@
       <c r="Y339" s="1"/>
       <c r="Z339" s="1"/>
       <c r="AA339" s="1"/>
-      <c r="AB339" s="1"/>
+      <c r="AB339" s="17"/>
       <c r="AC339" s="1"/>
       <c r="AD339" s="1"/>
       <c r="AE339" s="1"/>
@@ -23665,7 +23742,7 @@
       <c r="Y340" s="1"/>
       <c r="Z340" s="1"/>
       <c r="AA340" s="1"/>
-      <c r="AB340" s="1"/>
+      <c r="AB340" s="17"/>
       <c r="AC340" s="1"/>
       <c r="AD340" s="1"/>
       <c r="AE340" s="1"/>
@@ -23717,7 +23794,7 @@
       <c r="Y341" s="1"/>
       <c r="Z341" s="1"/>
       <c r="AA341" s="1"/>
-      <c r="AB341" s="1"/>
+      <c r="AB341" s="17"/>
       <c r="AC341" s="1"/>
       <c r="AD341" s="1"/>
       <c r="AE341" s="1"/>
@@ -23769,7 +23846,7 @@
       <c r="Y342" s="1"/>
       <c r="Z342" s="1"/>
       <c r="AA342" s="1"/>
-      <c r="AB342" s="1"/>
+      <c r="AB342" s="17"/>
       <c r="AC342" s="1"/>
       <c r="AD342" s="1"/>
       <c r="AE342" s="1"/>
@@ -23821,7 +23898,7 @@
       <c r="Y343" s="1"/>
       <c r="Z343" s="1"/>
       <c r="AA343" s="1"/>
-      <c r="AB343" s="1"/>
+      <c r="AB343" s="17"/>
       <c r="AC343" s="1"/>
       <c r="AD343" s="1"/>
       <c r="AE343" s="1"/>
@@ -23873,7 +23950,7 @@
       <c r="Y344" s="1"/>
       <c r="Z344" s="1"/>
       <c r="AA344" s="1"/>
-      <c r="AB344" s="1"/>
+      <c r="AB344" s="17"/>
       <c r="AC344" s="1"/>
       <c r="AD344" s="1"/>
       <c r="AE344" s="1"/>
@@ -23925,7 +24002,7 @@
       <c r="Y345" s="1"/>
       <c r="Z345" s="1"/>
       <c r="AA345" s="1"/>
-      <c r="AB345" s="1"/>
+      <c r="AB345" s="17"/>
       <c r="AC345" s="1"/>
       <c r="AD345" s="1"/>
       <c r="AE345" s="1"/>
@@ -23977,7 +24054,7 @@
       <c r="Y346" s="1"/>
       <c r="Z346" s="1"/>
       <c r="AA346" s="1"/>
-      <c r="AB346" s="1"/>
+      <c r="AB346" s="17"/>
       <c r="AC346" s="1"/>
       <c r="AD346" s="1"/>
       <c r="AE346" s="1"/>
@@ -24029,7 +24106,7 @@
       <c r="Y347" s="1"/>
       <c r="Z347" s="1"/>
       <c r="AA347" s="1"/>
-      <c r="AB347" s="1"/>
+      <c r="AB347" s="17"/>
       <c r="AC347" s="1"/>
       <c r="AD347" s="1"/>
       <c r="AE347" s="1"/>
@@ -24081,7 +24158,7 @@
       <c r="Y348" s="1"/>
       <c r="Z348" s="1"/>
       <c r="AA348" s="1"/>
-      <c r="AB348" s="1"/>
+      <c r="AB348" s="17"/>
       <c r="AC348" s="1"/>
       <c r="AD348" s="1"/>
       <c r="AE348" s="1"/>
@@ -24133,7 +24210,7 @@
       <c r="Y349" s="1"/>
       <c r="Z349" s="1"/>
       <c r="AA349" s="1"/>
-      <c r="AB349" s="1"/>
+      <c r="AB349" s="17"/>
       <c r="AC349" s="1"/>
       <c r="AD349" s="1"/>
       <c r="AE349" s="1"/>
@@ -24185,7 +24262,7 @@
       <c r="Y350" s="1"/>
       <c r="Z350" s="1"/>
       <c r="AA350" s="1"/>
-      <c r="AB350" s="1"/>
+      <c r="AB350" s="17"/>
       <c r="AC350" s="1"/>
       <c r="AD350" s="1"/>
       <c r="AE350" s="1"/>
@@ -24237,7 +24314,7 @@
       <c r="Y351" s="1"/>
       <c r="Z351" s="1"/>
       <c r="AA351" s="1"/>
-      <c r="AB351" s="1"/>
+      <c r="AB351" s="17"/>
       <c r="AC351" s="1"/>
       <c r="AD351" s="1"/>
       <c r="AE351" s="1"/>
@@ -24289,7 +24366,7 @@
       <c r="Y352" s="1"/>
       <c r="Z352" s="1"/>
       <c r="AA352" s="1"/>
-      <c r="AB352" s="1"/>
+      <c r="AB352" s="17"/>
       <c r="AC352" s="1"/>
       <c r="AD352" s="1"/>
       <c r="AE352" s="1"/>
@@ -24341,7 +24418,7 @@
       <c r="Y353" s="1"/>
       <c r="Z353" s="1"/>
       <c r="AA353" s="1"/>
-      <c r="AB353" s="1"/>
+      <c r="AB353" s="17"/>
       <c r="AC353" s="1"/>
       <c r="AD353" s="1"/>
       <c r="AE353" s="1"/>
@@ -24393,7 +24470,7 @@
       <c r="Y354" s="1"/>
       <c r="Z354" s="1"/>
       <c r="AA354" s="1"/>
-      <c r="AB354" s="1"/>
+      <c r="AB354" s="17"/>
       <c r="AC354" s="1"/>
       <c r="AD354" s="1"/>
       <c r="AE354" s="1"/>
@@ -24445,7 +24522,7 @@
       <c r="Y355" s="1"/>
       <c r="Z355" s="1"/>
       <c r="AA355" s="1"/>
-      <c r="AB355" s="1"/>
+      <c r="AB355" s="17"/>
       <c r="AC355" s="1"/>
       <c r="AD355" s="1"/>
       <c r="AE355" s="1"/>
@@ -24497,7 +24574,7 @@
       <c r="Y356" s="1"/>
       <c r="Z356" s="1"/>
       <c r="AA356" s="1"/>
-      <c r="AB356" s="1"/>
+      <c r="AB356" s="17"/>
       <c r="AC356" s="1"/>
       <c r="AD356" s="1"/>
       <c r="AE356" s="1"/>
@@ -24549,7 +24626,7 @@
       <c r="Y357" s="1"/>
       <c r="Z357" s="1"/>
       <c r="AA357" s="1"/>
-      <c r="AB357" s="1"/>
+      <c r="AB357" s="17"/>
       <c r="AC357" s="1"/>
       <c r="AD357" s="1"/>
       <c r="AE357" s="1"/>
@@ -24601,7 +24678,7 @@
       <c r="Y358" s="1"/>
       <c r="Z358" s="1"/>
       <c r="AA358" s="1"/>
-      <c r="AB358" s="1"/>
+      <c r="AB358" s="17"/>
       <c r="AC358" s="1"/>
       <c r="AD358" s="1"/>
       <c r="AE358" s="1"/>
@@ -24653,7 +24730,7 @@
       <c r="Y359" s="1"/>
       <c r="Z359" s="1"/>
       <c r="AA359" s="1"/>
-      <c r="AB359" s="1"/>
+      <c r="AB359" s="17"/>
       <c r="AC359" s="1"/>
       <c r="AD359" s="1"/>
       <c r="AE359" s="1"/>
@@ -24705,7 +24782,7 @@
       <c r="Y360" s="1"/>
       <c r="Z360" s="1"/>
       <c r="AA360" s="1"/>
-      <c r="AB360" s="1"/>
+      <c r="AB360" s="17"/>
       <c r="AC360" s="1"/>
       <c r="AD360" s="1"/>
       <c r="AE360" s="1"/>
@@ -24757,7 +24834,7 @@
       <c r="Y361" s="1"/>
       <c r="Z361" s="1"/>
       <c r="AA361" s="1"/>
-      <c r="AB361" s="1"/>
+      <c r="AB361" s="17"/>
       <c r="AC361" s="1"/>
       <c r="AD361" s="1"/>
       <c r="AE361" s="1"/>
@@ -24809,7 +24886,7 @@
       <c r="Y362" s="1"/>
       <c r="Z362" s="1"/>
       <c r="AA362" s="1"/>
-      <c r="AB362" s="1"/>
+      <c r="AB362" s="17"/>
       <c r="AC362" s="1"/>
       <c r="AD362" s="1"/>
       <c r="AE362" s="1"/>
@@ -24861,7 +24938,7 @@
       <c r="Y363" s="1"/>
       <c r="Z363" s="1"/>
       <c r="AA363" s="1"/>
-      <c r="AB363" s="1"/>
+      <c r="AB363" s="17"/>
       <c r="AC363" s="1"/>
       <c r="AD363" s="1"/>
       <c r="AE363" s="1"/>
@@ -24913,7 +24990,7 @@
       <c r="Y364" s="1"/>
       <c r="Z364" s="1"/>
       <c r="AA364" s="1"/>
-      <c r="AB364" s="1"/>
+      <c r="AB364" s="17"/>
       <c r="AC364" s="1"/>
       <c r="AD364" s="1"/>
       <c r="AE364" s="1"/>
@@ -24965,7 +25042,7 @@
       <c r="Y365" s="1"/>
       <c r="Z365" s="1"/>
       <c r="AA365" s="1"/>
-      <c r="AB365" s="1"/>
+      <c r="AB365" s="17"/>
       <c r="AC365" s="1"/>
       <c r="AD365" s="1"/>
       <c r="AE365" s="1"/>
@@ -25017,7 +25094,7 @@
       <c r="Y366" s="1"/>
       <c r="Z366" s="1"/>
       <c r="AA366" s="1"/>
-      <c r="AB366" s="1"/>
+      <c r="AB366" s="17"/>
       <c r="AC366" s="1"/>
       <c r="AD366" s="1"/>
       <c r="AE366" s="1"/>
@@ -25069,7 +25146,7 @@
       <c r="Y367" s="1"/>
       <c r="Z367" s="1"/>
       <c r="AA367" s="1"/>
-      <c r="AB367" s="1"/>
+      <c r="AB367" s="17"/>
       <c r="AC367" s="1"/>
       <c r="AD367" s="1"/>
       <c r="AE367" s="1"/>
@@ -25121,7 +25198,7 @@
       <c r="Y368" s="1"/>
       <c r="Z368" s="1"/>
       <c r="AA368" s="1"/>
-      <c r="AB368" s="1"/>
+      <c r="AB368" s="17"/>
       <c r="AC368" s="1"/>
       <c r="AD368" s="1"/>
       <c r="AE368" s="1"/>
@@ -25173,7 +25250,7 @@
       <c r="Y369" s="1"/>
       <c r="Z369" s="1"/>
       <c r="AA369" s="1"/>
-      <c r="AB369" s="1"/>
+      <c r="AB369" s="17"/>
       <c r="AC369" s="1"/>
       <c r="AD369" s="1"/>
       <c r="AE369" s="1"/>
@@ -25225,7 +25302,7 @@
       <c r="Y370" s="1"/>
       <c r="Z370" s="1"/>
       <c r="AA370" s="1"/>
-      <c r="AB370" s="1"/>
+      <c r="AB370" s="17"/>
       <c r="AC370" s="1"/>
       <c r="AD370" s="1"/>
       <c r="AE370" s="1"/>
@@ -25277,7 +25354,7 @@
       <c r="Y371" s="1"/>
       <c r="Z371" s="1"/>
       <c r="AA371" s="1"/>
-      <c r="AB371" s="1"/>
+      <c r="AB371" s="17"/>
       <c r="AC371" s="1"/>
       <c r="AD371" s="1"/>
       <c r="AE371" s="1"/>
@@ -25329,7 +25406,7 @@
       <c r="Y372" s="1"/>
       <c r="Z372" s="1"/>
       <c r="AA372" s="1"/>
-      <c r="AB372" s="1"/>
+      <c r="AB372" s="17"/>
       <c r="AC372" s="1"/>
       <c r="AD372" s="1"/>
       <c r="AE372" s="1"/>
@@ -25381,7 +25458,7 @@
       <c r="Y373" s="1"/>
       <c r="Z373" s="1"/>
       <c r="AA373" s="1"/>
-      <c r="AB373" s="1"/>
+      <c r="AB373" s="17"/>
       <c r="AC373" s="1"/>
       <c r="AD373" s="1"/>
       <c r="AE373" s="1"/>
@@ -25433,7 +25510,7 @@
       <c r="Y374" s="1"/>
       <c r="Z374" s="1"/>
       <c r="AA374" s="1"/>
-      <c r="AB374" s="1"/>
+      <c r="AB374" s="17"/>
       <c r="AC374" s="1"/>
       <c r="AD374" s="1"/>
       <c r="AE374" s="1"/>
@@ -25485,7 +25562,7 @@
       <c r="Y375" s="1"/>
       <c r="Z375" s="1"/>
       <c r="AA375" s="1"/>
-      <c r="AB375" s="1"/>
+      <c r="AB375" s="17"/>
       <c r="AC375" s="1"/>
       <c r="AD375" s="1"/>
       <c r="AE375" s="1"/>
@@ -25537,7 +25614,7 @@
       <c r="Y376" s="1"/>
       <c r="Z376" s="1"/>
       <c r="AA376" s="1"/>
-      <c r="AB376" s="1"/>
+      <c r="AB376" s="17"/>
       <c r="AC376" s="1"/>
       <c r="AD376" s="1"/>
       <c r="AE376" s="1"/>
@@ -25589,7 +25666,7 @@
       <c r="Y377" s="1"/>
       <c r="Z377" s="1"/>
       <c r="AA377" s="1"/>
-      <c r="AB377" s="1"/>
+      <c r="AB377" s="17"/>
       <c r="AC377" s="1"/>
       <c r="AD377" s="1"/>
       <c r="AE377" s="1"/>
@@ -25641,7 +25718,7 @@
       <c r="Y378" s="1"/>
       <c r="Z378" s="1"/>
       <c r="AA378" s="1"/>
-      <c r="AB378" s="1"/>
+      <c r="AB378" s="17"/>
       <c r="AC378" s="1"/>
       <c r="AD378" s="1"/>
       <c r="AE378" s="1"/>
@@ -25693,7 +25770,7 @@
       <c r="Y379" s="1"/>
       <c r="Z379" s="1"/>
       <c r="AA379" s="1"/>
-      <c r="AB379" s="1"/>
+      <c r="AB379" s="17"/>
       <c r="AC379" s="1"/>
       <c r="AD379" s="1"/>
       <c r="AE379" s="1"/>
@@ -25745,7 +25822,7 @@
       <c r="Y380" s="1"/>
       <c r="Z380" s="1"/>
       <c r="AA380" s="1"/>
-      <c r="AB380" s="1"/>
+      <c r="AB380" s="17"/>
       <c r="AC380" s="1"/>
       <c r="AD380" s="1"/>
       <c r="AE380" s="1"/>
@@ -25797,7 +25874,7 @@
       <c r="Y381" s="1"/>
       <c r="Z381" s="1"/>
       <c r="AA381" s="1"/>
-      <c r="AB381" s="1"/>
+      <c r="AB381" s="17"/>
       <c r="AC381" s="1"/>
       <c r="AD381" s="1"/>
       <c r="AE381" s="1"/>
@@ -25849,7 +25926,7 @@
       <c r="Y382" s="1"/>
       <c r="Z382" s="1"/>
       <c r="AA382" s="1"/>
-      <c r="AB382" s="1"/>
+      <c r="AB382" s="17"/>
       <c r="AC382" s="1"/>
       <c r="AD382" s="1"/>
       <c r="AE382" s="1"/>
@@ -25901,7 +25978,7 @@
       <c r="Y383" s="1"/>
       <c r="Z383" s="1"/>
       <c r="AA383" s="1"/>
-      <c r="AB383" s="1"/>
+      <c r="AB383" s="17"/>
       <c r="AC383" s="1"/>
       <c r="AD383" s="1"/>
       <c r="AE383" s="1"/>
@@ -25953,7 +26030,7 @@
       <c r="Y384" s="1"/>
       <c r="Z384" s="1"/>
       <c r="AA384" s="1"/>
-      <c r="AB384" s="1"/>
+      <c r="AB384" s="17"/>
       <c r="AC384" s="1"/>
       <c r="AD384" s="1"/>
       <c r="AE384" s="1"/>
@@ -26005,7 +26082,7 @@
       <c r="Y385" s="1"/>
       <c r="Z385" s="1"/>
       <c r="AA385" s="1"/>
-      <c r="AB385" s="1"/>
+      <c r="AB385" s="17"/>
       <c r="AC385" s="1"/>
       <c r="AD385" s="1"/>
       <c r="AE385" s="1"/>
@@ -26057,7 +26134,7 @@
       <c r="Y386" s="1"/>
       <c r="Z386" s="1"/>
       <c r="AA386" s="1"/>
-      <c r="AB386" s="1"/>
+      <c r="AB386" s="17"/>
       <c r="AC386" s="1"/>
       <c r="AD386" s="1"/>
       <c r="AE386" s="1"/>
@@ -26109,7 +26186,7 @@
       <c r="Y387" s="1"/>
       <c r="Z387" s="1"/>
       <c r="AA387" s="1"/>
-      <c r="AB387" s="1"/>
+      <c r="AB387" s="17"/>
       <c r="AC387" s="1"/>
       <c r="AD387" s="1"/>
       <c r="AE387" s="1"/>
@@ -26161,7 +26238,7 @@
       <c r="Y388" s="1"/>
       <c r="Z388" s="1"/>
       <c r="AA388" s="1"/>
-      <c r="AB388" s="1"/>
+      <c r="AB388" s="17"/>
       <c r="AC388" s="1"/>
       <c r="AD388" s="1"/>
       <c r="AE388" s="1"/>
@@ -26213,7 +26290,7 @@
       <c r="Y389" s="1"/>
       <c r="Z389" s="1"/>
       <c r="AA389" s="1"/>
-      <c r="AB389" s="1"/>
+      <c r="AB389" s="17"/>
       <c r="AC389" s="1"/>
       <c r="AD389" s="1"/>
       <c r="AE389" s="1"/>
@@ -26265,7 +26342,7 @@
       <c r="Y390" s="1"/>
       <c r="Z390" s="1"/>
       <c r="AA390" s="1"/>
-      <c r="AB390" s="1"/>
+      <c r="AB390" s="17"/>
       <c r="AC390" s="1"/>
       <c r="AD390" s="1"/>
       <c r="AE390" s="1"/>
@@ -26317,7 +26394,7 @@
       <c r="Y391" s="1"/>
       <c r="Z391" s="1"/>
       <c r="AA391" s="1"/>
-      <c r="AB391" s="1"/>
+      <c r="AB391" s="17"/>
       <c r="AC391" s="1"/>
       <c r="AD391" s="1"/>
       <c r="AE391" s="1"/>
@@ -26369,7 +26446,7 @@
       <c r="Y392" s="1"/>
       <c r="Z392" s="1"/>
       <c r="AA392" s="1"/>
-      <c r="AB392" s="1"/>
+      <c r="AB392" s="17"/>
       <c r="AC392" s="1"/>
       <c r="AD392" s="1"/>
       <c r="AE392" s="1"/>
@@ -26421,7 +26498,7 @@
       <c r="Y393" s="1"/>
       <c r="Z393" s="1"/>
       <c r="AA393" s="1"/>
-      <c r="AB393" s="1"/>
+      <c r="AB393" s="17"/>
       <c r="AC393" s="1"/>
       <c r="AD393" s="1"/>
       <c r="AE393" s="1"/>
@@ -26473,7 +26550,7 @@
       <c r="Y394" s="1"/>
       <c r="Z394" s="1"/>
       <c r="AA394" s="1"/>
-      <c r="AB394" s="1"/>
+      <c r="AB394" s="17"/>
       <c r="AC394" s="1"/>
       <c r="AD394" s="1"/>
       <c r="AE394" s="1"/>
@@ -26525,7 +26602,7 @@
       <c r="Y395" s="1"/>
       <c r="Z395" s="1"/>
       <c r="AA395" s="1"/>
-      <c r="AB395" s="1"/>
+      <c r="AB395" s="17"/>
       <c r="AC395" s="1"/>
       <c r="AD395" s="1"/>
       <c r="AE395" s="1"/>
@@ -26577,7 +26654,7 @@
       <c r="Y396" s="1"/>
       <c r="Z396" s="1"/>
       <c r="AA396" s="1"/>
-      <c r="AB396" s="1"/>
+      <c r="AB396" s="17"/>
       <c r="AC396" s="1"/>
       <c r="AD396" s="1"/>
       <c r="AE396" s="1"/>
@@ -26629,7 +26706,7 @@
       <c r="Y397" s="1"/>
       <c r="Z397" s="1"/>
       <c r="AA397" s="1"/>
-      <c r="AB397" s="1"/>
+      <c r="AB397" s="17"/>
       <c r="AC397" s="1"/>
       <c r="AD397" s="1"/>
       <c r="AE397" s="1"/>
@@ -26681,7 +26758,7 @@
       <c r="Y398" s="1"/>
       <c r="Z398" s="1"/>
       <c r="AA398" s="1"/>
-      <c r="AB398" s="1"/>
+      <c r="AB398" s="17"/>
       <c r="AC398" s="1"/>
       <c r="AD398" s="1"/>
       <c r="AE398" s="1"/>
@@ -26733,7 +26810,7 @@
       <c r="Y399" s="1"/>
       <c r="Z399" s="1"/>
       <c r="AA399" s="1"/>
-      <c r="AB399" s="1"/>
+      <c r="AB399" s="17"/>
       <c r="AC399" s="1"/>
       <c r="AD399" s="1"/>
       <c r="AE399" s="1"/>
@@ -26785,7 +26862,7 @@
       <c r="Y400" s="1"/>
       <c r="Z400" s="1"/>
       <c r="AA400" s="1"/>
-      <c r="AB400" s="1"/>
+      <c r="AB400" s="17"/>
       <c r="AC400" s="1"/>
       <c r="AD400" s="1"/>
       <c r="AE400" s="1"/>
@@ -26837,7 +26914,7 @@
       <c r="Y401" s="1"/>
       <c r="Z401" s="1"/>
       <c r="AA401" s="1"/>
-      <c r="AB401" s="1"/>
+      <c r="AB401" s="17"/>
       <c r="AC401" s="1"/>
       <c r="AD401" s="1"/>
       <c r="AE401" s="1"/>
@@ -26889,7 +26966,7 @@
       <c r="Y402" s="1"/>
       <c r="Z402" s="1"/>
       <c r="AA402" s="1"/>
-      <c r="AB402" s="1"/>
+      <c r="AB402" s="17"/>
       <c r="AC402" s="1"/>
       <c r="AD402" s="1"/>
       <c r="AE402" s="1"/>
@@ -26941,7 +27018,7 @@
       <c r="Y403" s="1"/>
       <c r="Z403" s="1"/>
       <c r="AA403" s="1"/>
-      <c r="AB403" s="1"/>
+      <c r="AB403" s="17"/>
       <c r="AC403" s="1"/>
       <c r="AD403" s="1"/>
       <c r="AE403" s="1"/>
@@ -26993,7 +27070,7 @@
       <c r="Y404" s="1"/>
       <c r="Z404" s="1"/>
       <c r="AA404" s="1"/>
-      <c r="AB404" s="1"/>
+      <c r="AB404" s="17"/>
       <c r="AC404" s="1"/>
       <c r="AD404" s="1"/>
       <c r="AE404" s="1"/>
@@ -27045,7 +27122,7 @@
       <c r="Y405" s="1"/>
       <c r="Z405" s="1"/>
       <c r="AA405" s="1"/>
-      <c r="AB405" s="1"/>
+      <c r="AB405" s="17"/>
       <c r="AC405" s="1"/>
       <c r="AD405" s="1"/>
       <c r="AE405" s="1"/>
@@ -27097,7 +27174,7 @@
       <c r="Y406" s="1"/>
       <c r="Z406" s="1"/>
       <c r="AA406" s="1"/>
-      <c r="AB406" s="1"/>
+      <c r="AB406" s="17"/>
       <c r="AC406" s="1"/>
       <c r="AD406" s="1"/>
       <c r="AE406" s="1"/>
@@ -27149,7 +27226,7 @@
       <c r="Y407" s="1"/>
       <c r="Z407" s="1"/>
       <c r="AA407" s="1"/>
-      <c r="AB407" s="1"/>
+      <c r="AB407" s="17"/>
       <c r="AC407" s="1"/>
       <c r="AD407" s="1"/>
       <c r="AE407" s="1"/>
@@ -27201,7 +27278,7 @@
       <c r="Y408" s="1"/>
       <c r="Z408" s="1"/>
       <c r="AA408" s="1"/>
-      <c r="AB408" s="1"/>
+      <c r="AB408" s="17"/>
       <c r="AC408" s="1"/>
       <c r="AD408" s="1"/>
       <c r="AE408" s="1"/>
@@ -27253,7 +27330,7 @@
       <c r="Y409" s="1"/>
       <c r="Z409" s="1"/>
       <c r="AA409" s="1"/>
-      <c r="AB409" s="1"/>
+      <c r="AB409" s="17"/>
       <c r="AC409" s="1"/>
       <c r="AD409" s="1"/>
       <c r="AE409" s="1"/>
@@ -27305,7 +27382,7 @@
       <c r="Y410" s="1"/>
       <c r="Z410" s="1"/>
       <c r="AA410" s="1"/>
-      <c r="AB410" s="1"/>
+      <c r="AB410" s="17"/>
       <c r="AC410" s="1"/>
       <c r="AD410" s="1"/>
       <c r="AE410" s="1"/>
@@ -27357,7 +27434,7 @@
       <c r="Y411" s="1"/>
       <c r="Z411" s="1"/>
       <c r="AA411" s="1"/>
-      <c r="AB411" s="1"/>
+      <c r="AB411" s="17"/>
       <c r="AC411" s="1"/>
       <c r="AD411" s="1"/>
       <c r="AE411" s="1"/>
@@ -27409,7 +27486,7 @@
       <c r="Y412" s="1"/>
       <c r="Z412" s="1"/>
       <c r="AA412" s="1"/>
-      <c r="AB412" s="1"/>
+      <c r="AB412" s="17"/>
       <c r="AC412" s="1"/>
       <c r="AD412" s="1"/>
       <c r="AE412" s="1"/>
@@ -27461,7 +27538,7 @@
       <c r="Y413" s="1"/>
       <c r="Z413" s="1"/>
       <c r="AA413" s="1"/>
-      <c r="AB413" s="1"/>
+      <c r="AB413" s="17"/>
       <c r="AC413" s="1"/>
       <c r="AD413" s="1"/>
       <c r="AE413" s="1"/>
@@ -27513,7 +27590,7 @@
       <c r="Y414" s="1"/>
       <c r="Z414" s="1"/>
       <c r="AA414" s="1"/>
-      <c r="AB414" s="1"/>
+      <c r="AB414" s="17"/>
       <c r="AC414" s="1"/>
       <c r="AD414" s="1"/>
       <c r="AE414" s="1"/>
@@ -27565,7 +27642,7 @@
       <c r="Y415" s="1"/>
       <c r="Z415" s="1"/>
       <c r="AA415" s="1"/>
-      <c r="AB415" s="1"/>
+      <c r="AB415" s="17"/>
       <c r="AC415" s="1"/>
       <c r="AD415" s="1"/>
       <c r="AE415" s="1"/>
@@ -27617,7 +27694,7 @@
       <c r="Y416" s="1"/>
       <c r="Z416" s="1"/>
       <c r="AA416" s="1"/>
-      <c r="AB416" s="1"/>
+      <c r="AB416" s="17"/>
       <c r="AC416" s="1"/>
       <c r="AD416" s="1"/>
       <c r="AE416" s="1"/>
@@ -27669,7 +27746,7 @@
       <c r="Y417" s="1"/>
       <c r="Z417" s="1"/>
       <c r="AA417" s="1"/>
-      <c r="AB417" s="1"/>
+      <c r="AB417" s="17"/>
       <c r="AC417" s="1"/>
       <c r="AD417" s="1"/>
       <c r="AE417" s="1"/>
@@ -27721,7 +27798,7 @@
       <c r="Y418" s="1"/>
       <c r="Z418" s="1"/>
       <c r="AA418" s="1"/>
-      <c r="AB418" s="1"/>
+      <c r="AB418" s="17"/>
       <c r="AC418" s="1"/>
       <c r="AD418" s="1"/>
       <c r="AE418" s="1"/>
@@ -27773,7 +27850,7 @@
       <c r="Y419" s="1"/>
       <c r="Z419" s="1"/>
       <c r="AA419" s="1"/>
-      <c r="AB419" s="1"/>
+      <c r="AB419" s="17"/>
       <c r="AC419" s="1"/>
       <c r="AD419" s="1"/>
       <c r="AE419" s="1"/>
@@ -27825,7 +27902,7 @@
       <c r="Y420" s="1"/>
       <c r="Z420" s="1"/>
       <c r="AA420" s="1"/>
-      <c r="AB420" s="1"/>
+      <c r="AB420" s="17"/>
       <c r="AC420" s="1"/>
       <c r="AD420" s="1"/>
       <c r="AE420" s="1"/>
@@ -27877,7 +27954,7 @@
       <c r="Y421" s="1"/>
       <c r="Z421" s="1"/>
       <c r="AA421" s="1"/>
-      <c r="AB421" s="1"/>
+      <c r="AB421" s="17"/>
       <c r="AC421" s="1"/>
       <c r="AD421" s="1"/>
       <c r="AE421" s="1"/>
@@ -27929,7 +28006,7 @@
       <c r="Y422" s="1"/>
       <c r="Z422" s="1"/>
       <c r="AA422" s="1"/>
-      <c r="AB422" s="1"/>
+      <c r="AB422" s="17"/>
       <c r="AC422" s="1"/>
       <c r="AD422" s="1"/>
       <c r="AE422" s="1"/>
@@ -27981,7 +28058,7 @@
       <c r="Y423" s="1"/>
       <c r="Z423" s="1"/>
       <c r="AA423" s="1"/>
-      <c r="AB423" s="1"/>
+      <c r="AB423" s="17"/>
       <c r="AC423" s="1"/>
       <c r="AD423" s="1"/>
       <c r="AE423" s="1"/>
@@ -28033,7 +28110,7 @@
       <c r="Y424" s="1"/>
       <c r="Z424" s="1"/>
       <c r="AA424" s="1"/>
-      <c r="AB424" s="1"/>
+      <c r="AB424" s="17"/>
       <c r="AC424" s="1"/>
       <c r="AD424" s="1"/>
       <c r="AE424" s="1"/>
@@ -28085,7 +28162,7 @@
       <c r="Y425" s="1"/>
       <c r="Z425" s="1"/>
       <c r="AA425" s="1"/>
-      <c r="AB425" s="1"/>
+      <c r="AB425" s="17"/>
       <c r="AC425" s="1"/>
       <c r="AD425" s="1"/>
       <c r="AE425" s="1"/>
@@ -28137,7 +28214,7 @@
       <c r="Y426" s="1"/>
       <c r="Z426" s="1"/>
       <c r="AA426" s="1"/>
-      <c r="AB426" s="1"/>
+      <c r="AB426" s="17"/>
       <c r="AC426" s="1"/>
       <c r="AD426" s="1"/>
       <c r="AE426" s="1"/>
@@ -28189,7 +28266,7 @@
       <c r="Y427" s="1"/>
       <c r="Z427" s="1"/>
       <c r="AA427" s="1"/>
-      <c r="AB427" s="1"/>
+      <c r="AB427" s="17"/>
       <c r="AC427" s="1"/>
       <c r="AD427" s="1"/>
       <c r="AE427" s="1"/>
@@ -28241,7 +28318,7 @@
       <c r="Y428" s="1"/>
       <c r="Z428" s="1"/>
       <c r="AA428" s="1"/>
-      <c r="AB428" s="1"/>
+      <c r="AB428" s="17"/>
       <c r="AC428" s="1"/>
       <c r="AD428" s="1"/>
       <c r="AE428" s="1"/>
@@ -28293,7 +28370,7 @@
       <c r="Y429" s="1"/>
       <c r="Z429" s="1"/>
       <c r="AA429" s="1"/>
-      <c r="AB429" s="1"/>
+      <c r="AB429" s="17"/>
       <c r="AC429" s="1"/>
       <c r="AD429" s="1"/>
       <c r="AE429" s="1"/>
@@ -28345,7 +28422,7 @@
       <c r="Y430" s="1"/>
       <c r="Z430" s="1"/>
       <c r="AA430" s="1"/>
-      <c r="AB430" s="1"/>
+      <c r="AB430" s="17"/>
       <c r="AC430" s="1"/>
       <c r="AD430" s="1"/>
       <c r="AE430" s="1"/>
@@ -28397,7 +28474,7 @@
       <c r="Y431" s="1"/>
       <c r="Z431" s="1"/>
       <c r="AA431" s="1"/>
-      <c r="AB431" s="1"/>
+      <c r="AB431" s="17"/>
       <c r="AC431" s="1"/>
       <c r="AD431" s="1"/>
       <c r="AE431" s="1"/>
@@ -28449,7 +28526,7 @@
       <c r="Y432" s="1"/>
       <c r="Z432" s="1"/>
       <c r="AA432" s="1"/>
-      <c r="AB432" s="1"/>
+      <c r="AB432" s="17"/>
       <c r="AC432" s="1"/>
       <c r="AD432" s="1"/>
       <c r="AE432" s="1"/>
@@ -28501,7 +28578,7 @@
       <c r="Y433" s="1"/>
       <c r="Z433" s="1"/>
       <c r="AA433" s="1"/>
-      <c r="AB433" s="1"/>
+      <c r="AB433" s="17"/>
       <c r="AC433" s="1"/>
       <c r="AD433" s="1"/>
       <c r="AE433" s="1"/>
@@ -28553,7 +28630,7 @@
       <c r="Y434" s="1"/>
       <c r="Z434" s="1"/>
       <c r="AA434" s="1"/>
-      <c r="AB434" s="1"/>
+      <c r="AB434" s="17"/>
       <c r="AC434" s="1"/>
       <c r="AD434" s="1"/>
       <c r="AE434" s="1"/>
@@ -28605,7 +28682,7 @@
       <c r="Y435" s="1"/>
       <c r="Z435" s="1"/>
       <c r="AA435" s="1"/>
-      <c r="AB435" s="1"/>
+      <c r="AB435" s="17"/>
       <c r="AC435" s="1"/>
       <c r="AD435" s="1"/>
       <c r="AE435" s="1"/>
@@ -28657,7 +28734,7 @@
       <c r="Y436" s="1"/>
       <c r="Z436" s="1"/>
       <c r="AA436" s="1"/>
-      <c r="AB436" s="1"/>
+      <c r="AB436" s="17"/>
       <c r="AC436" s="1"/>
       <c r="AD436" s="1"/>
       <c r="AE436" s="1"/>
@@ -28709,7 +28786,7 @@
       <c r="Y437" s="1"/>
       <c r="Z437" s="1"/>
       <c r="AA437" s="1"/>
-      <c r="AB437" s="1"/>
+      <c r="AB437" s="17"/>
       <c r="AC437" s="1"/>
       <c r="AD437" s="1"/>
       <c r="AE437" s="1"/>
@@ -28761,7 +28838,7 @@
       <c r="Y438" s="1"/>
       <c r="Z438" s="1"/>
       <c r="AA438" s="1"/>
-      <c r="AB438" s="1"/>
+      <c r="AB438" s="17"/>
       <c r="AC438" s="1"/>
       <c r="AD438" s="1"/>
       <c r="AE438" s="1"/>
@@ -28813,7 +28890,7 @@
       <c r="Y439" s="1"/>
       <c r="Z439" s="1"/>
       <c r="AA439" s="1"/>
-      <c r="AB439" s="1"/>
+      <c r="AB439" s="17"/>
       <c r="AC439" s="1"/>
       <c r="AD439" s="1"/>
       <c r="AE439" s="1"/>
@@ -28865,7 +28942,7 @@
       <c r="Y440" s="1"/>
       <c r="Z440" s="1"/>
       <c r="AA440" s="1"/>
-      <c r="AB440" s="1"/>
+      <c r="AB440" s="17"/>
       <c r="AC440" s="1"/>
       <c r="AD440" s="1"/>
       <c r="AE440" s="1"/>
@@ -28917,7 +28994,7 @@
       <c r="Y441" s="1"/>
       <c r="Z441" s="1"/>
       <c r="AA441" s="1"/>
-      <c r="AB441" s="1"/>
+      <c r="AB441" s="17"/>
       <c r="AC441" s="1"/>
       <c r="AD441" s="1"/>
       <c r="AE441" s="1"/>
@@ -28969,7 +29046,7 @@
       <c r="Y442" s="1"/>
       <c r="Z442" s="1"/>
       <c r="AA442" s="1"/>
-      <c r="AB442" s="1"/>
+      <c r="AB442" s="17"/>
       <c r="AC442" s="1"/>
       <c r="AD442" s="1"/>
       <c r="AE442" s="1"/>
@@ -29021,7 +29098,7 @@
       <c r="Y443" s="1"/>
       <c r="Z443" s="1"/>
       <c r="AA443" s="1"/>
-      <c r="AB443" s="1"/>
+      <c r="AB443" s="17"/>
       <c r="AC443" s="1"/>
       <c r="AD443" s="1"/>
       <c r="AE443" s="1"/>
@@ -29073,7 +29150,7 @@
       <c r="Y444" s="1"/>
       <c r="Z444" s="1"/>
       <c r="AA444" s="1"/>
-      <c r="AB444" s="1"/>
+      <c r="AB444" s="17"/>
       <c r="AC444" s="1"/>
       <c r="AD444" s="1"/>
       <c r="AE444" s="1"/>
@@ -29125,7 +29202,7 @@
       <c r="Y445" s="1"/>
       <c r="Z445" s="1"/>
       <c r="AA445" s="1"/>
-      <c r="AB445" s="1"/>
+      <c r="AB445" s="17"/>
       <c r="AC445" s="1"/>
       <c r="AD445" s="1"/>
       <c r="AE445" s="1"/>
@@ -29177,7 +29254,7 @@
       <c r="Y446" s="1"/>
       <c r="Z446" s="1"/>
       <c r="AA446" s="1"/>
-      <c r="AB446" s="1"/>
+      <c r="AB446" s="17"/>
       <c r="AC446" s="1"/>
       <c r="AD446" s="1"/>
       <c r="AE446" s="1"/>
@@ -29229,7 +29306,7 @@
       <c r="Y447" s="1"/>
       <c r="Z447" s="1"/>
       <c r="AA447" s="1"/>
-      <c r="AB447" s="1"/>
+      <c r="AB447" s="17"/>
       <c r="AC447" s="1"/>
       <c r="AD447" s="1"/>
       <c r="AE447" s="1"/>
@@ -29281,7 +29358,7 @@
       <c r="Y448" s="1"/>
       <c r="Z448" s="1"/>
       <c r="AA448" s="1"/>
-      <c r="AB448" s="1"/>
+      <c r="AB448" s="17"/>
       <c r="AC448" s="1"/>
       <c r="AD448" s="1"/>
       <c r="AE448" s="1"/>
@@ -29333,7 +29410,7 @@
       <c r="Y449" s="1"/>
       <c r="Z449" s="1"/>
       <c r="AA449" s="1"/>
-      <c r="AB449" s="1"/>
+      <c r="AB449" s="17"/>
       <c r="AC449" s="1"/>
       <c r="AD449" s="1"/>
       <c r="AE449" s="1"/>
@@ -29385,7 +29462,7 @@
       <c r="Y450" s="1"/>
       <c r="Z450" s="1"/>
       <c r="AA450" s="1"/>
-      <c r="AB450" s="1"/>
+      <c r="AB450" s="17"/>
       <c r="AC450" s="1"/>
       <c r="AD450" s="1"/>
       <c r="AE450" s="1"/>
@@ -29437,7 +29514,7 @@
       <c r="Y451" s="1"/>
       <c r="Z451" s="1"/>
       <c r="AA451" s="1"/>
-      <c r="AB451" s="1"/>
+      <c r="AB451" s="17"/>
       <c r="AC451" s="1"/>
       <c r="AD451" s="1"/>
       <c r="AE451" s="1"/>
@@ -29489,7 +29566,7 @@
       <c r="Y452" s="1"/>
       <c r="Z452" s="1"/>
       <c r="AA452" s="1"/>
-      <c r="AB452" s="1"/>
+      <c r="AB452" s="17"/>
       <c r="AC452" s="1"/>
       <c r="AD452" s="1"/>
       <c r="AE452" s="1"/>
@@ -29541,7 +29618,7 @@
       <c r="Y453" s="1"/>
       <c r="Z453" s="1"/>
       <c r="AA453" s="1"/>
-      <c r="AB453" s="1"/>
+      <c r="AB453" s="17"/>
       <c r="AC453" s="1"/>
       <c r="AD453" s="1"/>
       <c r="AE453" s="1"/>
@@ -29593,7 +29670,7 @@
       <c r="Y454" s="1"/>
       <c r="Z454" s="1"/>
       <c r="AA454" s="1"/>
-      <c r="AB454" s="1"/>
+      <c r="AB454" s="17"/>
       <c r="AC454" s="1"/>
       <c r="AD454" s="1"/>
       <c r="AE454" s="1"/>
@@ -29645,7 +29722,7 @@
       <c r="Y455" s="1"/>
       <c r="Z455" s="1"/>
       <c r="AA455" s="1"/>
-      <c r="AB455" s="1"/>
+      <c r="AB455" s="17"/>
       <c r="AC455" s="1"/>
       <c r="AD455" s="1"/>
       <c r="AE455" s="1"/>
@@ -29697,7 +29774,7 @@
       <c r="Y456" s="1"/>
       <c r="Z456" s="1"/>
       <c r="AA456" s="1"/>
-      <c r="AB456" s="1"/>
+      <c r="AB456" s="17"/>
       <c r="AC456" s="1"/>
       <c r="AD456" s="1"/>
       <c r="AE456" s="1"/>
@@ -29749,7 +29826,7 @@
       <c r="Y457" s="1"/>
       <c r="Z457" s="1"/>
       <c r="AA457" s="1"/>
-      <c r="AB457" s="1"/>
+      <c r="AB457" s="17"/>
       <c r="AC457" s="1"/>
       <c r="AD457" s="1"/>
       <c r="AE457" s="1"/>
@@ -29801,7 +29878,7 @@
       <c r="Y458" s="1"/>
       <c r="Z458" s="1"/>
       <c r="AA458" s="1"/>
-      <c r="AB458" s="1"/>
+      <c r="AB458" s="17"/>
       <c r="AC458" s="1"/>
       <c r="AD458" s="1"/>
       <c r="AE458" s="1"/>
@@ -29853,7 +29930,7 @@
       <c r="Y459" s="1"/>
       <c r="Z459" s="1"/>
       <c r="AA459" s="1"/>
-      <c r="AB459" s="1"/>
+      <c r="AB459" s="17"/>
       <c r="AC459" s="1"/>
       <c r="AD459" s="1"/>
       <c r="AE459" s="1"/>
@@ -29905,7 +29982,7 @@
       <c r="Y460" s="1"/>
       <c r="Z460" s="1"/>
       <c r="AA460" s="1"/>
-      <c r="AB460" s="1"/>
+      <c r="AB460" s="17"/>
       <c r="AC460" s="1"/>
       <c r="AD460" s="1"/>
       <c r="AE460" s="1"/>
@@ -29957,7 +30034,7 @@
       <c r="Y461" s="1"/>
       <c r="Z461" s="1"/>
       <c r="AA461" s="1"/>
-      <c r="AB461" s="1"/>
+      <c r="AB461" s="17"/>
       <c r="AC461" s="1"/>
       <c r="AD461" s="1"/>
       <c r="AE461" s="1"/>
@@ -30009,7 +30086,7 @@
       <c r="Y462" s="1"/>
       <c r="Z462" s="1"/>
       <c r="AA462" s="1"/>
-      <c r="AB462" s="1"/>
+      <c r="AB462" s="17"/>
       <c r="AC462" s="1"/>
       <c r="AD462" s="1"/>
       <c r="AE462" s="1"/>
@@ -30061,7 +30138,7 @@
       <c r="Y463" s="1"/>
       <c r="Z463" s="1"/>
       <c r="AA463" s="1"/>
-      <c r="AB463" s="1"/>
+      <c r="AB463" s="17"/>
       <c r="AC463" s="1"/>
       <c r="AD463" s="1"/>
       <c r="AE463" s="1"/>
@@ -30113,7 +30190,7 @@
       <c r="Y464" s="1"/>
       <c r="Z464" s="1"/>
       <c r="AA464" s="1"/>
-      <c r="AB464" s="1"/>
+      <c r="AB464" s="17"/>
       <c r="AC464" s="1"/>
       <c r="AD464" s="1"/>
       <c r="AE464" s="1"/>
@@ -30165,7 +30242,7 @@
       <c r="Y465" s="1"/>
       <c r="Z465" s="1"/>
       <c r="AA465" s="1"/>
-      <c r="AB465" s="1"/>
+      <c r="AB465" s="17"/>
       <c r="AC465" s="1"/>
       <c r="AD465" s="1"/>
       <c r="AE465" s="1"/>
@@ -30217,7 +30294,7 @@
       <c r="Y466" s="1"/>
       <c r="Z466" s="1"/>
       <c r="AA466" s="1"/>
-      <c r="AB466" s="1"/>
+      <c r="AB466" s="17"/>
       <c r="AC466" s="1"/>
       <c r="AD466" s="1"/>
       <c r="AE466" s="1"/>
@@ -30269,7 +30346,7 @@
       <c r="Y467" s="1"/>
       <c r="Z467" s="1"/>
       <c r="AA467" s="1"/>
-      <c r="AB467" s="1"/>
+      <c r="AB467" s="17"/>
       <c r="AC467" s="1"/>
       <c r="AD467" s="1"/>
       <c r="AE467" s="1"/>
@@ -30321,7 +30398,7 @@
       <c r="Y468" s="1"/>
       <c r="Z468" s="1"/>
       <c r="AA468" s="1"/>
-      <c r="AB468" s="1"/>
+      <c r="AB468" s="17"/>
       <c r="AC468" s="1"/>
       <c r="AD468" s="1"/>
       <c r="AE468" s="1"/>
@@ -30373,7 +30450,7 @@
       <c r="Y469" s="1"/>
       <c r="Z469" s="1"/>
       <c r="AA469" s="1"/>
-      <c r="AB469" s="1"/>
+      <c r="AB469" s="17"/>
       <c r="AC469" s="1"/>
       <c r="AD469" s="1"/>
       <c r="AE469" s="1"/>
@@ -30425,7 +30502,7 @@
       <c r="Y470" s="1"/>
       <c r="Z470" s="1"/>
       <c r="AA470" s="1"/>
-      <c r="AB470" s="1"/>
+      <c r="AB470" s="17"/>
       <c r="AC470" s="1"/>
       <c r="AD470" s="1"/>
       <c r="AE470" s="1"/>
@@ -30477,7 +30554,7 @@
       <c r="Y471" s="1"/>
       <c r="Z471" s="1"/>
       <c r="AA471" s="1"/>
-      <c r="AB471" s="1"/>
+      <c r="AB471" s="17"/>
       <c r="AC471" s="1"/>
       <c r="AD471" s="1"/>
       <c r="AE471" s="1"/>
@@ -30529,7 +30606,7 @@
       <c r="Y472" s="1"/>
       <c r="Z472" s="1"/>
       <c r="AA472" s="1"/>
-      <c r="AB472" s="1"/>
+      <c r="AB472" s="17"/>
       <c r="AC472" s="1"/>
       <c r="AD472" s="1"/>
       <c r="AE472" s="1"/>
@@ -30581,7 +30658,7 @@
       <c r="Y473" s="1"/>
       <c r="Z473" s="1"/>
       <c r="AA473" s="1"/>
-      <c r="AB473" s="1"/>
+      <c r="AB473" s="17"/>
       <c r="AC473" s="1"/>
       <c r="AD473" s="1"/>
       <c r="AE473" s="1"/>
@@ -30633,7 +30710,7 @@
       <c r="Y474" s="1"/>
       <c r="Z474" s="1"/>
       <c r="AA474" s="1"/>
-      <c r="AB474" s="1"/>
+      <c r="AB474" s="17"/>
       <c r="AC474" s="1"/>
       <c r="AD474" s="1"/>
       <c r="AE474" s="1"/>
@@ -30685,7 +30762,7 @@
       <c r="Y475" s="1"/>
       <c r="Z475" s="1"/>
       <c r="AA475" s="1"/>
-      <c r="AB475" s="1"/>
+      <c r="AB475" s="17"/>
       <c r="AC475" s="1"/>
       <c r="AD475" s="1"/>
       <c r="AE475" s="1"/>
@@ -30737,7 +30814,7 @@
       <c r="Y476" s="1"/>
       <c r="Z476" s="1"/>
       <c r="AA476" s="1"/>
-      <c r="AB476" s="1"/>
+      <c r="AB476" s="17"/>
       <c r="AC476" s="1"/>
       <c r="AD476" s="1"/>
       <c r="AE476" s="1"/>
@@ -30789,7 +30866,7 @@
       <c r="Y477" s="1"/>
       <c r="Z477" s="1"/>
       <c r="AA477" s="1"/>
-      <c r="AB477" s="1"/>
+      <c r="AB477" s="17"/>
       <c r="AC477" s="1"/>
       <c r="AD477" s="1"/>
       <c r="AE477" s="1"/>
@@ -30841,7 +30918,7 @@
       <c r="Y478" s="1"/>
       <c r="Z478" s="1"/>
       <c r="AA478" s="1"/>
-      <c r="AB478" s="1"/>
+      <c r="AB478" s="17"/>
       <c r="AC478" s="1"/>
       <c r="AD478" s="1"/>
       <c r="AE478" s="1"/>
@@ -30893,7 +30970,7 @@
       <c r="Y479" s="1"/>
       <c r="Z479" s="1"/>
       <c r="AA479" s="1"/>
-      <c r="AB479" s="1"/>
+      <c r="AB479" s="17"/>
       <c r="AC479" s="1"/>
       <c r="AD479" s="1"/>
       <c r="AE479" s="1"/>
@@ -30945,7 +31022,7 @@
       <c r="Y480" s="1"/>
       <c r="Z480" s="1"/>
       <c r="AA480" s="1"/>
-      <c r="AB480" s="1"/>
+      <c r="AB480" s="17"/>
       <c r="AC480" s="1"/>
       <c r="AD480" s="1"/>
       <c r="AE480" s="1"/>
@@ -30997,7 +31074,7 @@
       <c r="Y481" s="1"/>
       <c r="Z481" s="1"/>
       <c r="AA481" s="1"/>
-      <c r="AB481" s="1"/>
+      <c r="AB481" s="17"/>
       <c r="AC481" s="1"/>
       <c r="AD481" s="1"/>
       <c r="AE481" s="1"/>
@@ -31049,7 +31126,7 @@
       <c r="Y482" s="1"/>
       <c r="Z482" s="1"/>
       <c r="AA482" s="1"/>
-      <c r="AB482" s="1"/>
+      <c r="AB482" s="17"/>
       <c r="AC482" s="1"/>
       <c r="AD482" s="1"/>
       <c r="AE482" s="1"/>
@@ -31101,7 +31178,7 @@
       <c r="Y483" s="1"/>
       <c r="Z483" s="1"/>
       <c r="AA483" s="1"/>
-      <c r="AB483" s="1"/>
+      <c r="AB483" s="17"/>
       <c r="AC483" s="1"/>
       <c r="AD483" s="1"/>
       <c r="AE483" s="1"/>
@@ -31153,7 +31230,7 @@
       <c r="Y484" s="1"/>
       <c r="Z484" s="1"/>
       <c r="AA484" s="1"/>
-      <c r="AB484" s="1"/>
+      <c r="AB484" s="17"/>
       <c r="AC484" s="1"/>
       <c r="AD484" s="1"/>
       <c r="AE484" s="1"/>
@@ -31205,7 +31282,7 @@
       <c r="Y485" s="1"/>
       <c r="Z485" s="1"/>
       <c r="AA485" s="1"/>
-      <c r="AB485" s="1"/>
+      <c r="AB485" s="17"/>
       <c r="AC485" s="1"/>
       <c r="AD485" s="1"/>
       <c r="AE485" s="1"/>
@@ -31257,7 +31334,7 @@
       <c r="Y486" s="1"/>
       <c r="Z486" s="1"/>
       <c r="AA486" s="1"/>
-      <c r="AB486" s="1"/>
+      <c r="AB486" s="17"/>
       <c r="AC486" s="1"/>
       <c r="AD486" s="1"/>
       <c r="AE486" s="1"/>
@@ -31309,7 +31386,7 @@
       <c r="Y487" s="1"/>
       <c r="Z487" s="1"/>
       <c r="AA487" s="1"/>
-      <c r="AB487" s="1"/>
+      <c r="AB487" s="17"/>
       <c r="AC487" s="1"/>
       <c r="AD487" s="1"/>
       <c r="AE487" s="1"/>
@@ -31361,7 +31438,7 @@
       <c r="Y488" s="1"/>
       <c r="Z488" s="1"/>
       <c r="AA488" s="1"/>
-      <c r="AB488" s="1"/>
+      <c r="AB488" s="17"/>
       <c r="AC488" s="1"/>
       <c r="AD488" s="1"/>
       <c r="AE488" s="1"/>
@@ -31413,7 +31490,7 @@
       <c r="Y489" s="1"/>
       <c r="Z489" s="1"/>
       <c r="AA489" s="1"/>
-      <c r="AB489" s="1"/>
+      <c r="AB489" s="17"/>
       <c r="AC489" s="1"/>
       <c r="AD489" s="1"/>
       <c r="AE489" s="1"/>
@@ -31465,7 +31542,7 @@
       <c r="Y490" s="1"/>
       <c r="Z490" s="1"/>
       <c r="AA490" s="1"/>
-      <c r="AB490" s="1"/>
+      <c r="AB490" s="17"/>
       <c r="AC490" s="1"/>
       <c r="AD490" s="1"/>
       <c r="AE490" s="1"/>
@@ -31517,7 +31594,7 @@
       <c r="Y491" s="1"/>
       <c r="Z491" s="1"/>
       <c r="AA491" s="1"/>
-      <c r="AB491" s="1"/>
+      <c r="AB491" s="17"/>
       <c r="AC491" s="1"/>
       <c r="AD491" s="1"/>
       <c r="AE491" s="1"/>
@@ -31569,7 +31646,7 @@
       <c r="Y492" s="1"/>
       <c r="Z492" s="1"/>
       <c r="AA492" s="1"/>
-      <c r="AB492" s="1"/>
+      <c r="AB492" s="17"/>
       <c r="AC492" s="1"/>
       <c r="AD492" s="1"/>
       <c r="AE492" s="1"/>
@@ -31621,7 +31698,7 @@
       <c r="Y493" s="1"/>
       <c r="Z493" s="1"/>
       <c r="AA493" s="1"/>
-      <c r="AB493" s="1"/>
+      <c r="AB493" s="17"/>
       <c r="AC493" s="1"/>
       <c r="AD493" s="1"/>
       <c r="AE493" s="1"/>
@@ -31673,7 +31750,7 @@
       <c r="Y494" s="1"/>
       <c r="Z494" s="1"/>
       <c r="AA494" s="1"/>
-      <c r="AB494" s="1"/>
+      <c r="AB494" s="17"/>
       <c r="AC494" s="1"/>
       <c r="AD494" s="1"/>
       <c r="AE494" s="1"/>
@@ -31725,7 +31802,7 @@
       <c r="Y495" s="1"/>
       <c r="Z495" s="1"/>
       <c r="AA495" s="1"/>
-      <c r="AB495" s="1"/>
+      <c r="AB495" s="17"/>
       <c r="AC495" s="1"/>
       <c r="AD495" s="1"/>
       <c r="AE495" s="1"/>
@@ -31777,7 +31854,7 @@
       <c r="Y496" s="1"/>
       <c r="Z496" s="1"/>
       <c r="AA496" s="1"/>
-      <c r="AB496" s="1"/>
+      <c r="AB496" s="17"/>
       <c r="AC496" s="1"/>
       <c r="AD496" s="1"/>
       <c r="AE496" s="1"/>
@@ -31829,7 +31906,7 @@
       <c r="Y497" s="1"/>
       <c r="Z497" s="1"/>
       <c r="AA497" s="1"/>
-      <c r="AB497" s="1"/>
+      <c r="AB497" s="17"/>
       <c r="AC497" s="1"/>
       <c r="AD497" s="1"/>
       <c r="AE497" s="1"/>
